--- a/帝国时代2决定版 文明联盟 发育经济流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 发育经济流最优研究顺序 By RemonBo.xlsx
@@ -2544,7 +2544,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>直接强化经济</t>
+          <t>采集效率提升，经济成型更快</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>直接强化经济</t>
+          <t>采集效率提升，经济成型更快</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>直接强化经济</t>
+          <t>采集效率提升，经济成型更快</t>
         </is>
       </c>
     </row>
@@ -2679,14 +2679,14 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>直接强化经济</t>
+          <t>机动性提升</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -2706,14 +2706,14 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>直接强化经济</t>
+          <t>工作速度提升，成型更快</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -2738,9 +2738,9 @@
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -2765,9 +2765,9 @@
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -2787,14 +2787,14 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>额外产出资源，经济滚雪球更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -2814,14 +2814,14 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>直接强化经济</t>
+          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -2846,9 +2846,9 @@
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -2868,14 +2868,14 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>直接强化经济</t>
+          <t>额外获得村民，开局更宽裕</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -2895,2012 +2895,2012 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
+          <t>市场/贸易收益提升，黄金来得更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>房屋/聚落人口+5</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>人口容量提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>城堡起步兵铁匠铺升级影响村民</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>狂热/圣洁影响村民</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>胡斯革新（僧侣和修道院科技消耗黄金而非食物）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
           <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>房屋/聚落人口+5</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>市场效率 +80%</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>村民封建/城堡/帝王每分钟恢复10/15/20生命</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>石矿工产石料+黄金</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>额外产出资源，经济滚雪球更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>开局每种资源+25</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>村民可驻聚落</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>可驻扎，受攻击时更安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>塔楼和城堡提供的人口空间 +10</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>研究科技获黄金+20</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>贸易单位产生的黄金 +25%</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>市场/贸易收益提升，黄金来得更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>斯巴达</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>村民/捕鱼船存食+10%</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>资源存放上限提升，少跑几趟</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>斯巴达</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>训练速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>斯拉夫</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>农民工作速度+15%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>斯拉夫</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>斯拉夫</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>军事建筑 (城堡除外) 提供的人口空间 +5</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>高棉</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>农民无需磨坊/TC即可存食</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>资源存放上限提升，少跑几趟</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>高棉</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>村民可驻房</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>可驻扎，受攻击时更安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>印度斯坦</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>大干道（所有黄金收入速度+10%；市场交易费降至10%）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>市场/贸易收益提升，黄金来得更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>哥特</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>猎人携带+15，猎物持续+20%</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>携带量提升，往返次数更少</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>哥特</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>帝王人口+10</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>人口容量提升</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>羊倌/猎人采食时缓慢产金</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>额外产出资源，经济滚雪球更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>蒙古</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>猎人速度+40%</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>蒙古</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>游牧（失去房屋时人口不减）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>人口容量提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>萨拉森</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>市场贸易税仅5%</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>市场/贸易收益提升，黄金来得更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>萨拉森</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>市场木材-100</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>市场/贸易收益提升，黄金来得更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>渔夫/捕鱼船携带+15</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>升时代木材+200</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>城堡起步兵铁匠铺升级影响村民</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>码头提供的人口空间 +5</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>格鲁吉亚</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>强化教堂使9格内村民效率+10%</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>狂热/圣洁影响村民</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>阿兹特克</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>初始黄金+50</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>胡斯革新（僧侣和修道院科技消耗黄金而非食物）</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>阿兹特克</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>村民携带量+3</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>携带量提升，往返次数更少</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>阿兹特克</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>圣物产生的黄金 +33%</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>采果工存食+25%</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>聚落可训长矛/掷矛</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>骑兵杀敌+3黄金</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>捕鱼船/村民存食+5%</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>资源存放上限提升，少跑几趟</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>摧毁建筑抢25%资源</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>雅典</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>伐木工缓慢产食</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>雅典</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>军役税（希腊步兵黄金50%改为额外食物）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>市场效率 +80%</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>女真</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>爆炸/溅射范围提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>马里</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>村民存金+10%</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>资源存放上限提升，少跑几趟</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>玛雅</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>开局村民+1，食物-50</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>玛雅</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>资源持续+15%</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>采果工产食+木材</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>西西里</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>初始石料+100</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>西西里</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>农田升级食物+125%</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>经济升级无木材且研究+100%</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>纸币（伐木工产木并缓慢产金）</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>不列颠</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>羊倌工作速度+25%</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>村民收集/建造/修理速度+5%</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>马来</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>村民一击杀狼</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>一击必杀，反骚扰更省心</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="28" customHeight="1">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>采果工速度+15%</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="28" customHeight="1">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>村民黑暗移速+5%，封建起+10%</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>凯尔特</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>伐木工速度+15%</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>伐木工产木+食物</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>土耳其</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>金矿工速度+25%</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="28" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>穆伊斯卡</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>天然黄金资源持续时间 +15%</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>村民封建/城堡/帝王每分钟恢复10/15/20生命</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="28" customHeight="1">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>契丹</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>牧场取代农田</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>石矿工产石料+黄金</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>解锁升级形态，本流派的上限更高</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="28" customHeight="1">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>初始木材/食物+50</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E83" s="4" t="inlineStr">
         <is>
           <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>开局每种资源+25</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+    <row r="84" ht="28" customHeight="1">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="28" customHeight="1">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>升时代获得黄金+100、食物+100</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E85" s="4" t="inlineStr">
         <is>
           <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>村民可驻聚落</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>哨站视野 +3 且不消耗石料</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>视野提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="28" customHeight="1">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>匈奴</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>不需要房屋，但初始木材-100</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>塔楼和城堡提供的人口空间 +10</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>人口容量提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>西班牙</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>研究科技获黄金+20</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="28" customHeight="1">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>库曼</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>靶场/马厩木材-75</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E88" s="4" t="inlineStr">
         <is>
           <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>西班牙</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>西班牙</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>贸易单位产生的黄金 +25%</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
+    <row r="89" ht="28" customHeight="1">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>立陶宛</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>每座TC食物+100</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>村民/捕鱼船存食+10%</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+    <row r="90" ht="28" customHeight="1">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>撒克逊人</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>磨坊/木料/采矿场建成后食物+35，石料+10</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>斯拉夫</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>农民工作速度+15%</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="28" customHeight="1">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>瓦兰吉人</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>牧羊/捕鱼/狩猎也产黄金</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>建造/工作效率提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>斯拉夫</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>斯拉夫</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>军事建筑 (城堡除外) 提供的人口空间 +5</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>人口容量提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>高棉</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>农民无需磨坊/TC即可存食</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>高棉</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>村民可驻房</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>印度斯坦</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>大干道（所有黄金收入速度+10%；市场交易费降至10%）</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>哥特</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>猎人携带+15，猎物持续+20%</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>哥特</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>帝王人口+10</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>人口容量提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>羊倌/猎人采食时缓慢产金</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>蒙古</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>猎人速度+40%</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>蒙古</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>游牧（失去房屋时人口不减）</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>人口容量提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>萨拉森</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>市场贸易税仅5%</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>萨拉森</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>市场木材-100</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>达罗毗荼</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>渔夫/捕鱼船携带+15</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>达罗毗荼</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>升时代木材+200</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>达罗毗荼</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>码头提供的人口空间 +5</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>人口容量提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>格鲁吉亚</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>强化教堂使9格内村民效率+10%</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>初始黄金+50</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>村民携带量+3</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>圣物产生的黄金 +33%</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>马普切</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>采果工存食+25%</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>马普切</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>聚落可训长矛/掷矛</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>马普切</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>骑兵杀敌+3黄金</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>捕鱼船/村民存食+5%</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>摧毁建筑抢25%资源</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>伐木工缓慢产食</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="28" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>军役税（希腊步兵黄金50%改为额外食物）</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="28" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>女真</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>爆炸/溅射范围提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>马里</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>村民存金+10%</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>玛雅</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>开局村民+1，食物-50</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>玛雅</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>资源持续+15%</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>葡萄牙</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>采果工产食+木材</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="28" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>西西里</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>初始石料+100</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>西西里</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>农田升级食物+125%</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="28" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>越南</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>经济升级无木材且研究+100%</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="28" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>越南</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>纸币（伐木工产木并缓慢产金）</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="28" customHeight="1">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>不列颠</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>羊倌工作速度+25%</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>建造/工作效率提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="28" customHeight="1">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>村民收集/建造/修理速度+5%</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>建造/工作效率提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="28" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>马来</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="28" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>马扎尔</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>村民一击杀狼</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="28" customHeight="1">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>马扎尔</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="28" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>法兰克</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>采果工速度+15%</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="28" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>柏柏尔</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>村民黑暗移速+5%，封建起+10%</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>机动性提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="28" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>凯尔特</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>伐木工速度+15%</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="28" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>蜀</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>伐木工产木+食物</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="28" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>土耳其</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>金矿工速度+25%</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="28" customHeight="1">
-      <c r="A81" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>穆伊斯卡</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>天然黄金资源持续时间 +15%</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="28" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>契丹</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>牧场取代农田</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="28" customHeight="1">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>初始木材/食物+50</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="28" customHeight="1">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="28" customHeight="1">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>升时代获得黄金+100、食物+100</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="28" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>哨站视野 +3 且不消耗石料</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>视野提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="28" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>匈奴</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>不需要房屋，但初始木材-100</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="28" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>库曼</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>靶场/马厩木材-75</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="28" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>立陶宛</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>每座TC食物+100</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="28" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>撒克逊人</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>磨坊/木料/采矿场建成后食物+35，石料+10</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="28" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>瓦兰吉人</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>牧羊/捕鱼/狩猎也产黄金</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>资源产出/节省，加快成型</t>
+          <t>采集效率提升，经济成型更快</t>
         </is>
       </c>
     </row>
     <row r="92" ht="28" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4975,812 +4975,812 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>维京</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>独轮推车/手推车免费</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>免费获得，等于直接省下这笔支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>远程/步兵木材费用-50%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>战船木材-20%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>可提前一个时代经济升级且食物-40%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>孟加拉</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>大乘佛教（村民/僧侣人口-10%）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>建筑石料-15%</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>铁匠铺/大学木材费用-100</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>维京</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>独轮推车/手推车免费</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>血统/斥候食物费用-50%</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>免费获得，等于直接省下这笔支出</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>高丽</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>远程/步兵木材费用-50%</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>贵族特权（骑士黄金费用-60%）</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>靶场/兵营升级食物-50%</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>高丽</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>战船木材-20%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>印度斯坦</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>村民黑暗/封建/城堡/帝王费用-8/13/18/23%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>勃艮第</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>可提前一个时代经济升级且食物-40%</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>攻城武器木材-33%</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>孟加拉</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>大乘佛教（村民/僧侣人口-10%）</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>格鲁吉亚</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>阿兹瑙里骑兵（骑兵人口-20%）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>人口容量提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>建筑石料-15%</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>兵营/攻城武器厂黄金升级-66%</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>铁匠铺/大学木材费用-100</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>女真</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>攻城/防御工事升级木材-75%，研究+100%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>血统/斥候食物费用-50%</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>马里</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>建筑木材-15%</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>贵族特权（骑士黄金费用-60%）</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>不列颠</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>城堡起TC木材费用-50%</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>蝎式弩黄金-50%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>马来</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>养鱼场费用-33%且食物+200%</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>靶场/兵营升级食物-50%</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>条顿</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>农田费用-40%</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>印度斯坦</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>村民黑暗/封建/城堡/帝王费用-8/13/18/23%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>意大利</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>丝绸之路（贸易单位费用-50%）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>魏</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>每研究一次经济升级免费获一村民</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>穆伊斯卡</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>升时代黄金-50%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>达罗毗荼</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>攻城武器木材-33%</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>穆伊斯卡</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>聚落成本-33%且治疗附近</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>格鲁吉亚</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>阿兹瑙里骑兵（骑兵人口-20%）</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>保加利亚</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>保加利亚</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>TC石料费用-50%</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>匈奴</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>无神论（敌方圣物产资源-50%；奇观/圣物胜利倒计时+100年）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>人口容量提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>兵营/攻城武器厂黄金升级-66%</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>女真</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>攻城/防御工事升级木材-75%，研究+100%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>马里</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>建筑木材-15%</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>葡萄牙</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>所有单位黄金费用-20%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>不列颠</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>城堡起TC木材费用-50%</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>瞿折罗</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>刹帝利（军事单位食物-25%）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>蝎式弩黄金-50%</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>马来</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>养鱼场费用-33%且食物+200%</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>法兰克</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>条顿</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>农田费用-40%</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>意大利</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>丝绸之路（贸易单位费用-50%）</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>魏</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>每研究一次经济升级免费获一村民</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>穆伊斯卡</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>升时代黄金-50%</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>穆伊斯卡</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>聚落成本-33%且治疗附近</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>保加利亚</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>保加利亚</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>TC石料费用-50%</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>匈奴</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>无神论（敌方圣物产资源-50%；奇观/圣物胜利倒计时+100年）</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>瞿折罗</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>刹帝利（军事单位食物-25%）</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>

--- a/帝国时代2决定版 文明联盟 发育经济流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 发育经济流最优研究顺序 By RemonBo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开局3免费位" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后续2000金顺序" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="甲类·经济本体强化" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·科技与前置" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·减费用与资源效率" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="与发育经济流无关·可跳过" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主选文明推荐" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全62文明总名次" sheetId="7" state="visible" r:id="rId7"/>
@@ -20,10 +20,10 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$55</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·经济本体强化'!$A$1:$E$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·经济本体强化'!$A$1:$E$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·经济本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·科技与前置'!$A$1:$E$31</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·科技与前置'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$83</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与发育经济流无关·可跳过'!$A$1:$D$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与发育经济流无关·可跳过'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$16</definedName>
@@ -574,7 +574,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="51" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>第 1 位</t>
@@ -587,12 +587,12 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>初始村民+3，木材-50，食物-200；TC视野+7，人口+15；火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
+          <t>火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 4 / 弱 0）；经济科技树 16/18；缺 轮作、行会；最直接一条：初始村民+3，木材-50，食物-200</t>
+          <t>阶段1·本体强化；原生条目 8 条（强 4 / 弱 0）；经济科技树 16/18；缺 轮作、行会；最直接一条：初始村民+3，木材-50，食物-200</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 5 条（强 3 / 弱 0）；经济科技树 17/18；缺 轮作；最直接一条：石矿工速度+20%</t>
+          <t>备选：阶段1·本体强化；原生条目 8 条（强 3 / 弱 0）；经济科技树 17/18；缺 轮作；最直接一条：石矿工速度+20%</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 4 条（强 2 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：勃艮第葡萄园（农民产食并缓慢产金）</t>
+          <t>备选：阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：勃艮第葡萄园（农民产食并缓慢产金）</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：独轮推车/手推车免费</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：独轮推车/手推车免费</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 3 条（强 3 / 弱 0）；经济科技树 17/18；缺 采石场；最直接一条：升时代TC产生2村民</t>
+          <t>备选：阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；经济科技树 17/18；缺 采石场；最直接一条：升时代TC产生2村民</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 4 条（强 2 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：房屋/聚落人口+5</t>
+          <t>备选：阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：房屋/聚落人口+5</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 4 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：采石村民缓慢获食</t>
+          <t>阶段1·本体强化；原生条目 8 条（强 4 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：采石村民缓慢获食</t>
         </is>
       </c>
     </row>
@@ -718,11 +718,11 @@
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 5 条（强 2 / 弱 1）；经济科技树 17/18；缺 轮作；最直接一条：狂热/圣洁影响村民</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
+          <t>备选：阶段1·本体强化；原生条目 7 条（强 2 / 弱 1）；经济科技树 17/18；缺 轮作；最直接一条：狂热/圣洁影响村民</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="51" customHeight="1">
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 5 条（强 2 / 弱 1）；经济科技树 15/18；缺 双人锯、钻井采金法、行会；最直接一条：村民封建/城堡/帝王每分钟恢复10/15/20生命</t>
+          <t>备选：阶段1·本体强化；原生条目 7 条（强 2 / 弱 1）；经济科技树 15/18；缺 双人锯、钻井采金法、行会；最直接一条：村民封建/城堡/帝王每分钟恢复10/15/20生命</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>石矿工速度+20%；远程/步兵木材费用-50%；战船木材-20%</t>
+          <t>石矿工速度+20%；神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）；战船木材-20%</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 5 条（强 3 / 弱 0）；经济科技树 17/18；缺 轮作；最直接一条：石矿工速度+20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 8 条（强 3 / 弱 0）；经济科技树 17/18；缺 轮作；最直接一条：石矿工速度+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>5</v>
       </c>
@@ -843,7 +843,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>可提前一个时代经济升级且食物-40%；勃艮第葡萄园（农民产食并缓慢产金）；弗拉芒革命（所有村民变弗拉芒民兵）</t>
+          <t>可提前一个时代经济升级且食物-40%；圣物不仅能产生黄金，还能产生食物</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 2 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：勃艮第葡萄园（农民产食并缓慢产金）</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：勃艮第葡萄园（农民产食并缓慢产金）</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3 / 弱 0）；经济科技树 17/18；缺 采石场；最直接一条：升时代TC产生2村民</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；经济科技树 17/18；缺 采石场；最直接一条：升时代TC产生2村民</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>房屋/聚落人口+5；建筑石料-15%；军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%</t>
+          <t>建筑石料-15%；军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 2 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：房屋/聚落人口+5</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：房屋/聚落人口+5</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>铁匠铺/大学木材费用-100；狂热/圣洁影响村民；胡斯革新（僧侣和修道院科技消耗黄金而非食物）</t>
+          <t>胡斯革新（僧侣和修道院科技消耗黄金而非食物）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -943,11 +943,11 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 5 条（强 2 / 弱 1）；经济科技树 17/18；缺 轮作；最直接一条：狂热/圣洁影响村民</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 7 条（强 2 / 弱 1）；经济科技树 17/18；缺 轮作；最直接一条：狂热/圣洁影响村民</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="51" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>9</v>
       </c>
@@ -963,7 +963,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>村民封建/城堡/帝王每分钟恢复10/15/20生命；石矿工产石料+黄金；血统/斥候食物费用-50%</t>
+          <t>石矿工产石料+黄金</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 5 条（强 2 / 弱 1）；经济科技树 15/18；缺 双人锯、钻井采金法、行会；最直接一条：村民封建/城堡/帝王每分钟恢复10/15/20生命</t>
+          <t>阶段1·本体强化；原生条目 7 条（强 2 / 弱 1）；经济科技树 15/18；缺 双人锯、钻井采金法、行会；最直接一条：村民封建/城堡/帝王每分钟恢复10/15/20生命</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>开局每种资源+25；村民可驻聚落；靶场/兵营升级食物-50%</t>
+          <t>靶场/兵营升级食物-50%</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、行会；最直接一条：村民可驻聚落</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、行会；最直接一条：村民可驻聚落</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>研究科技获黄金+20；霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）；贸易单位产生的黄金 +25%</t>
+          <t>研究科技获黄金+20</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、钻井采金法；最直接一条：霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、钻井采金法；最直接一条：霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>村民/捕鱼船存食+10%；希洛人征兵（长矛/掷矛/村民训练+50%）</t>
+          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：村民/捕鱼船存食+10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：村民/捕鱼船存食+10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>13</v>
       </c>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>农民工作速度+15%；罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）；军事建筑 (城堡除外) 提供的人口空间 +5</t>
+          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：农民工作速度+15%</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：农民工作速度+15%</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：农民无需磨坊/TC即可存食</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：农民无需磨坊/TC即可存食</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>村民黑暗/封建/城堡/帝王费用-8/13/18/23%；大干道（所有黄金收入速度+10%；市场交易费降至10%）</t>
+          <t>村民黑暗/封建/城堡/帝王费用-8/13/18/23%</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、行会；最直接一条：村民黑暗/封建/城堡/帝王费用-8/13/18/23%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、行会；最直接一条：村民黑暗/封建/城堡/帝王费用-8/13/18/23%</t>
         </is>
       </c>
     </row>
@@ -1183,11 +1183,11 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：猎人携带+15，猎物持续+20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：猎人携带+15，猎物持续+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="51" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>17</v>
       </c>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、双人锯；最直接一条：堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、双人锯；最直接一条：堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、双人锯、行会；最直接一条：猎人速度+40%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、双人锯、行会；最直接一条：猎人速度+40%</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、行会；最直接一条：市场贸易税仅5%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、行会；最直接一条：市场贸易税仅5%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>渔夫/捕鱼船携带+15；升时代木材+200；攻城武器木材-33%</t>
+          <t>升时代木材+200；攻城武器木材-33%</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 1 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、钻井采金法；最直接一条：码头提供的人口空间 +5</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 1 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、钻井采金法；最直接一条：码头提供的人口空间 +5</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；经济科技树 16/18；缺 双人锯、钻井采金法；最直接一条：强化教堂使9格内村民效率+10%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 双人锯、钻井采金法；最直接一条：强化教堂使9格内村民效率+10%</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>初始黄金+50；村民携带量+3；圣物产生的黄金 +33%</t>
+          <t>初始黄金+50；圣物产生的黄金 +33%</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：村民携带量+3</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：村民携带量+3</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：采果工存食+25%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：采果工存食+25%</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>捕鱼船/村民存食+5%；摧毁建筑抢25%资源；兵营/攻城武器厂黄金升级-66%</t>
+          <t>兵营/攻城武器厂黄金升级-66%</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 0）；经济科技树 15/18；缺 轮作、双人锯、行会；最直接一条：捕鱼船/村民存食+5%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 0）；经济科技树 15/18；缺 轮作、双人锯、行会；最直接一条：捕鱼船/村民存食+5%</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>伐木工缓慢产食；军役税（希腊步兵黄金50%改为额外食物）</t>
+          <t>军役税（希腊步兵黄金50%改为额外食物）；TC可切换政策风格（经济/海军/军事）</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 1）；经济科技树 18/18（无缺项）；最直接一条：伐木工缓慢产食</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 1）；经济科技树 18/18（无缺项）；最直接一条：伐木工缓慢产食</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>攻城/防御工事升级木材-75%，研究+100%；霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）；攻城/防御工事升级木材-75%，研究+100%</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>建筑木材-15%；村民存金+10%</t>
+          <t>建筑木材-15%</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：村民存金+10%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：村民存金+10%</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：开局村民+1，食物-50</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：开局村民+1，食物-50</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>采果工产食+木材；所有单位黄金费用-20%</t>
+          <t>采果工产食+木材</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：采果工产食+木材</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：采果工产食+木材</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>初始石料+100；农田升级食物+125%</t>
+          <t>初始石料+100</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：农田升级食物+125%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：农田升级食物+125%</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>经济升级无木材且研究+100%；纸币（伐木工产木并缓慢产金）</t>
+          <t>经济升级无木材且研究+100%</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：纸币（伐木工产木并缓慢产金）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：纸币（伐木工产木并缓慢产金）</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>羊倌工作速度+25%；城堡起TC木材费用-50%</t>
+          <t>城堡起TC木材费用-50%</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：羊倌工作速度+25%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：羊倌工作速度+25%</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>村民收集/建造/修理速度+5%；蝎式弩黄金-50%</t>
+          <t>蝎式弩黄金-50%</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、采石场；最直接一条：村民收集/建造/修理速度+5%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、采石场；最直接一条：村民收集/建造/修理速度+5%</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>养鱼场费用-33%且食物+200%；强征兵役（生产民兵系消耗额外食物而非黄金）</t>
+          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：养鱼场费用-33%且食物+200%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：养鱼场费用-33%且食物+200%</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>村民一击杀狼；科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：村民一击杀狼</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：村民一击杀狼</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 1）；经济科技树 15/18；缺 双人锯、采石场、行会；最直接一条：采果工速度+15%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 1）；经济科技树 15/18；缺 双人锯、采石场、行会；最直接一条：采果工速度+15%</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：村民黑暗移速+5%，封建起+10%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：村民黑暗移速+5%，封建起+10%</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：农田费用-40%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：农田费用-40%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：丝绸之路（贸易单位费用-50%）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：丝绸之路（贸易单位费用-50%）</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、双人锯；最直接一条：伐木工速度+15%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、双人锯；最直接一条：伐木工速度+15%</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：伐木工产木+食物</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：伐木工产木+食物</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：金矿工速度+25%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：金矿工速度+25%</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：每研究一次经济升级免费获一村民</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：每研究一次经济升级免费获一村民</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>升时代黄金-50%；聚落成本-33%且治疗附近；天然黄金资源持续时间 +15%</t>
+          <t>升时代黄金-50%；篷车/行会免费</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 0 / 弱 1）；经济科技树 18/18（无缺项）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 0 / 弱 1）；经济科技树 18/18（无缺项）</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；经济科技树 14/18；缺 重犁、重犁升级、轮作、钻井采金法；最直接一条：牧场取代农田</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 14/18；缺 重犁、重犁升级、轮作、钻井采金法；最直接一条：牧场取代农田</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 0）；经济科技树 18/18（无缺项）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 18/18（无缺项）</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 0）；经济科技树 17/18；缺 轮作</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 17/18；缺 轮作</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 0）；经济科技树 17/18；缺 双人锯</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 17/18；缺 双人锯</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>不需要房屋，但初始木材-100；无神论（敌方圣物产资源-50%；奇观/圣物胜利倒计时+100年）</t>
+          <t>不需要房屋，但初始木材-100</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -2173,11 +2173,11 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 0）；经济科技树 16/18；缺 轮作、采石场</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 16/18；缺 轮作、采石场</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>50</v>
       </c>
@@ -2203,11 +2203,11 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 采石场</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 采石场</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>51</v>
       </c>
@@ -2233,11 +2233,11 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 钻井采金法</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 钻井采金法</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>52</v>
       </c>
@@ -2263,11 +2263,11 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 采石场</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 采石场</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>53</v>
       </c>
@@ -2293,11 +2293,11 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 钻井采金法</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 钻井采金法</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>54</v>
       </c>
@@ -2323,11 +2323,11 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 轮作</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 轮作</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>55</v>
       </c>
@@ -2353,11 +2353,11 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 1）；经济科技树 16/18；缺 双人锯、行会</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 1）；经济科技树 16/18；缺 双人锯、行会</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>56</v>
       </c>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；经济科技树 17/18；缺 采石场</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="28" customHeight="1">
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；经济科技树 17/18；缺 采石场</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>57</v>
       </c>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；经济科技树 16/18；缺 轮作、采石场</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；经济科技树 16/18；缺 轮作、采石场</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2480,206 +2480,206 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>初始村民+3，木材-50，食物-200</t>
+          <t>火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>石矿工速度+20%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>射程提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>战船木材-20%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>可提前一个时代经济升级且食物-40%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>圣物不仅能产生黄金，还能产生食物</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
           <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>中国</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>TC视野+7，人口+15</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>视野提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>中国</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>中国</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>农田的食物 +10%</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>普鲁人</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>采石村民缓慢获食</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>普鲁人</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>村民/捕鱼船采牡蛎+15%</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>吠陀教义（翰林院每项科技使村民效率+2%，最大20%）</t>
+          <t>建筑石料-15%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>采集效率提升，经济成型更快</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>贸易车移动速度 +15%</t>
+          <t>军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>机动性提升</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
@@ -2691,2241 +2691,1053 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>石矿工速度+20%</t>
+          <t>胡斯革新（僧侣和修道院科技消耗黄金而非食物）</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>石矿工产石料+黄金</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>额外产出资源，经济滚雪球更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>靶场/兵营升级食物-50%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>研究科技获黄金+20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>斯巴达</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>训练速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>升时代木材+200</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>攻城武器木材-33%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>阿兹特克</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>初始黄金+50</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>阿兹特克</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>圣物产生的黄金 +33%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>采果工存食+25%</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>聚落可训长矛/掷矛</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>骑兵杀敌+3黄金</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>兵营/攻城武器厂黄金升级-66%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>雅典</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>军役税（希腊步兵黄金50%改为额外食物）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>雅典</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>TC可切换政策风格（经济/海军/军事）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>可切换政策风格，按局势临时调整</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>女真</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>爆炸/溅射范围提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>女真</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>攻城/防御工事升级木材-75%，研究+100%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>马里</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>建筑木材-15%</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>采果工产食+木材</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>西西里</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>初始石料+100</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>经济升级无木材且研究+100%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>蝎式弩黄金-50%</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>马来</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>采果工速度+15%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>土耳其</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>金矿工速度+25%</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
           <t>工作速度提升，成型更快</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>高丽</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>穆伊斯卡</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>升时代黄金-50%</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>穆伊斯卡</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>篷车/行会免费</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>免费获得，等于直接省下这笔支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>初始木材/食物+50</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>射程提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>高丽</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>村民视野 +3</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>升时代获得黄金+100、食物+100</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>哨站视野 +3 且不消耗石料</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>视野提升</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>勃艮第</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>勃艮第葡萄园（农民产食并缓慢产金）</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>匈奴</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>不需要房屋，但初始木材-100</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>库曼</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>靶场/马厩木材-75</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>立陶宛</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>每座TC食物+100</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>瓦兰吉人</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>牧羊/捕鱼/狩猎也产黄金</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>吴</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>军事建筑/码头建成后食物+55</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>瞿折罗</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>刹帝利（军事单位食物-25%）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>额外产出资源，经济滚雪球更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>勃艮第</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>弗拉芒革命（所有村民变弗拉芒民兵）</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>勃艮第</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>圣物不仅能产生黄金，还能产生食物</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>孟加拉</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>升时代TC产生2村民</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>额外获得村民，开局更宽裕</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>孟加拉</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>贸易单位不仅能产生黄金，还能额外产生 10% 的食物</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>市场/贸易收益提升，黄金来得更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>房屋/聚落人口+5</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>人口容量提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>城堡起步兵铁匠铺升级影响村民</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>狂热/圣洁影响村民</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>胡斯革新（僧侣和修道院科技消耗黄金而非食物）</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>市场效率 +80%</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>村民封建/城堡/帝王每分钟恢复10/15/20生命</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>石矿工产石料+黄金</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>额外产出资源，经济滚雪球更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>开局每种资源+25</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>村民可驻聚落</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>可驻扎，受攻击时更安全</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>塔楼和城堡提供的人口空间 +10</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>西班牙</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>研究科技获黄金+20</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>西班牙</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>西班牙</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>贸易单位产生的黄金 +25%</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>市场/贸易收益提升，黄金来得更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>村民/捕鱼船存食+10%</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>资源存放上限提升，少跑几趟</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>训练速度提升，成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>斯拉夫</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>农民工作速度+15%</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>工作速度提升，成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>斯拉夫</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>斯拉夫</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>军事建筑 (城堡除外) 提供的人口空间 +5</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>高棉</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>农民无需磨坊/TC即可存食</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>资源存放上限提升，少跑几趟</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>高棉</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>村民可驻房</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>可驻扎，受攻击时更安全</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>印度斯坦</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>大干道（所有黄金收入速度+10%；市场交易费降至10%）</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>市场/贸易收益提升，黄金来得更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>哥特</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>猎人携带+15，猎物持续+20%</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>携带量提升，往返次数更少</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>哥特</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>帝王人口+10</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>人口容量提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>羊倌/猎人采食时缓慢产金</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>额外产出资源，经济滚雪球更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>蒙古</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>猎人速度+40%</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>工作速度提升，成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>蒙古</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>游牧（失去房屋时人口不减）</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>人口容量提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>萨拉森</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>市场贸易税仅5%</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>市场/贸易收益提升，黄金来得更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>萨拉森</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>市场木材-100</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>市场/贸易收益提升，黄金来得更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>达罗毗荼</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>渔夫/捕鱼船携带+15</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>达罗毗荼</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>升时代木材+200</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="36" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>达罗毗荼</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>码头提供的人口空间 +5</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>格鲁吉亚</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>强化教堂使9格内村民效率+10%</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>初始黄金+50</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>村民携带量+3</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>携带量提升，往返次数更少</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>圣物产生的黄金 +33%</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>马普切</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>采果工存食+25%</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="36" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>马普切</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>聚落可训长矛/掷矛</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>马普切</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>骑兵杀敌+3黄金</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>捕鱼船/村民存食+5%</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>资源存放上限提升，少跑几趟</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>摧毁建筑抢25%资源</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>伐木工缓慢产食</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="28" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>军役税（希腊步兵黄金50%改为额外食物）</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="28" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>女真</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>爆炸/溅射范围提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>马里</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>村民存金+10%</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>资源存放上限提升，少跑几趟</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>玛雅</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>开局村民+1，食物-50</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>玛雅</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>资源持续+15%</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>葡萄牙</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>采果工产食+木材</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="28" customHeight="1">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>西西里</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>初始石料+100</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>西西里</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>农田升级食物+125%</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="28" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>越南</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>经济升级无木材且研究+100%</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="28" customHeight="1">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>越南</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>纸币（伐木工产木并缓慢产金）</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="28" customHeight="1">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>不列颠</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>羊倌工作速度+25%</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>工作速度提升，成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="28" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>村民收集/建造/修理速度+5%</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>工作速度提升，成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="28" customHeight="1">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>马来</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="28" customHeight="1">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>马扎尔</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>村民一击杀狼</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>一击必杀，反骚扰更省心</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="28" customHeight="1">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>马扎尔</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="28" customHeight="1">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>法兰克</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>采果工速度+15%</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="28" customHeight="1">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>柏柏尔</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>村民黑暗移速+5%，封建起+10%</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>机动性提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="28" customHeight="1">
-      <c r="A78" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>凯尔特</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>伐木工速度+15%</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="28" customHeight="1">
-      <c r="A79" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>蜀</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>伐木工产木+食物</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="28" customHeight="1">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>土耳其</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>金矿工速度+25%</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>工作速度提升，成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="28" customHeight="1">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>穆伊斯卡</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>天然黄金资源持续时间 +15%</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="28" customHeight="1">
-      <c r="A82" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>契丹</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>牧场取代农田</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>解锁升级形态，本流派的上限更高</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="28" customHeight="1">
-      <c r="A83" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>初始木材/食物+50</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="28" customHeight="1">
-      <c r="A84" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="28" customHeight="1">
-      <c r="A85" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>升时代获得黄金+100、食物+100</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="28" customHeight="1">
-      <c r="A86" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>哨站视野 +3 且不消耗石料</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>视野提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="28" customHeight="1">
-      <c r="A87" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>匈奴</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>不需要房屋，但初始木材-100</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="28" customHeight="1">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>库曼</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>靶场/马厩木材-75</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="28" customHeight="1">
-      <c r="A89" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>立陶宛</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>每座TC食物+100</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="28" customHeight="1">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>撒克逊人</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>磨坊/木料/采矿场建成后食物+35，石料+10</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="28" customHeight="1">
-      <c r="A91" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>瓦兰吉人</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>牧羊/捕鱼/狩猎也产黄金</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="28" customHeight="1">
-      <c r="A92" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>吴</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>军事建筑/码头建成后食物+55</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E92"/>
+  <autoFilter ref="A1:E48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -4937,7 +3749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4982,810 +3794,2214 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>初始村民+3，木材-50，食物-200</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>TC视野+7，人口+15</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>视野提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>农田的食物 +10%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>维京</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>独轮推车/手推车免费</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>免费获得，等于直接省下这笔支出</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>普鲁人</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>采石村民缓慢获食</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>普鲁人</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>村民/捕鱼船采牡蛎+15%</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>普鲁人</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>吠陀教义（翰林院每项科技使村民效率+2%，最大20%）</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>普鲁人</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>贸易车移动速度 +15%</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>高丽</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>远程/步兵木材费用-50%</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>高丽</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>战船木材-20%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>村民视野 +3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>视野提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>勃艮第葡萄园（农民产食并缓慢产金）</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>额外产出资源，经济滚雪球更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>弗拉芒革命（所有村民变弗拉芒民兵）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>孟加拉</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>升时代TC产生2村民</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>额外获得村民，开局更宽裕</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>孟加拉</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>大乘佛教（村民/僧侣人口-10%）</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>勃艮第</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>可提前一个时代经济升级且食物-40%</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>提前解锁，抢一个时代的节奏</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>孟加拉</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>贸易单位不仅能产生黄金，还能额外产生 10% 的食物</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>市场/贸易收益提升，黄金来得更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>孟加拉</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>大乘佛教（村民/僧侣人口-10%）</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>房屋/聚落人口+5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>人口容量提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>城堡起步兵铁匠铺升级影响村民</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>铁匠铺/大学木材费用-100</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>采矿场科技免费</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>狂热/圣洁影响村民</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>市场效率 +80%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>血统/斥候食物费用-50%</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>贵族特权（骑士黄金费用-60%）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>建筑石料-15%</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>村民封建/城堡/帝王每分钟恢复10/15/20生命</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>大庄园替代磨坊</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>直接强化经济</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>村民可驻聚落</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>可驻扎，受攻击时更安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>塔楼和城堡提供的人口空间 +10</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>开局每种资源+25</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>贸易单位产生的黄金 +25%</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>市场/贸易收益提升，黄金来得更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>斯巴达</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>村民/捕鱼船存食+10%</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>资源存放上限提升，少跑几趟</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>斯拉夫</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>斯拉夫</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>农民工作速度+15%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>斯拉夫</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>军事建筑 (城堡除外) 提供的人口空间 +5</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>高棉</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>农民无需磨坊/TC即可存食</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>资源存放上限提升，少跑几趟</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>高棉</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>村民可驻房</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>可驻扎，受攻击时更安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>印度斯坦</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>村民黑暗/封建/城堡/帝王费用-8/13/18/23%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>铁匠铺/大学木材费用-100</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>印度斯坦</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>大干道（所有黄金收入速度+10%；市场交易费降至10%）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>市场/贸易收益提升，黄金来得更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>哥特</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>猎人携带+15，猎物持续+20%</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>携带量提升，往返次数更少</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>哥特</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>帝王人口+10</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>人口容量提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>羊倌/猎人采食时缓慢产金</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>额外产出资源，经济滚雪球更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>蒙古</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>猎人速度+40%</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>蒙古</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>游牧（失去房屋时人口不减）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>人口容量提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>萨拉森</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>市场贸易税仅5%</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>市场/贸易收益提升，黄金来得更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>萨拉森</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>市场木材-100</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>市场/贸易收益提升，黄金来得更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>码头提供的人口空间 +5</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>渔夫/捕鱼船携带+15</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>格鲁吉亚</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>强化教堂使9格内村民效率+10%</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>格鲁吉亚</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>阿兹瑙里骑兵（骑兵人口-20%）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>血统/斥候食物费用-50%</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>阿兹特克</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>村民携带量+3</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>携带量提升，往返次数更少</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>捕鱼船/村民存食+5%</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>资源存放上限提升，少跑几趟</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>摧毁建筑抢25%资源</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>雅典</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>伐木工缓慢产食</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>马里</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>村民存金+10%</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>资源存放上限提升，少跑几趟</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>玛雅</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>开局村民+1，食物-50</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>玛雅</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>资源持续+15%</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>贵族特权（骑士黄金费用-60%）</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>西西里</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>农田升级食物+125%</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>纸币（伐木工产木并缓慢产金）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>不列颠</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>城堡起TC木材费用-50%</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>靶场/兵营升级食物-50%</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>不列颠</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>羊倌工作速度+25%</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>村民收集/建造/修理速度+5%</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>马来</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>养鱼场费用-33%且食物+200%</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>印度斯坦</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>村民黑暗/封建/城堡/帝王费用-8/13/18/23%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>村民一击杀狼</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>一击必杀，反骚扰更省心</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="36" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>磨坊科技免费</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>村民黑暗移速+5%，封建起+10%</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>条顿</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>农田费用-40%</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>达罗毗荼</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>攻城武器木材-33%</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>意大利</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>丝绸之路（贸易单位费用-50%）</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>格鲁吉亚</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>阿兹瑙里骑兵（骑兵人口-20%）</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>凯尔特</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>伐木工速度+15%</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>伐木工产木+食物</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="36" customHeight="1">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>魏</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>每研究一次经济升级免费获一村民</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>穆伊斯卡</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>聚落成本-33%且治疗附近</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="28" customHeight="1">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>穆伊斯卡</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>天然黄金资源持续时间 +15%</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>契丹</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>牧场取代农田</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>解锁升级形态，本流派的上限更高</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="28" customHeight="1">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>保加利亚</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>保加利亚</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>TC石料费用-50%</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>匈奴</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>无神论（敌方圣物产资源-50%；奇观/圣物胜利倒计时+100年）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>兵营/攻城武器厂黄金升级-66%</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>撒克逊人</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>磨坊/木料/采矿场建成后食物+35，石料+10</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="28" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>瞿折罗</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>牲畜驻磨坊被动产食</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>额外产出资源，经济滚雪球更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>缅甸</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>伐木场科技免费</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="28" customHeight="1">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>磨坊/伐木场/采矿场费用-50%</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>女真</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>攻城/防御工事升级木材-75%，研究+100%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>马里</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>建筑木材-15%</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>葡萄牙</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>所有单位黄金费用-20%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>不列颠</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>城堡起TC木材费用-50%</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>蝎式弩黄金-50%</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>马来</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>养鱼场费用-33%且食物+200%</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>法兰克</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>条顿</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>农田费用-40%</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>意大利</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>丝绸之路（贸易单位费用-50%）</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>魏</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>每研究一次经济升级免费获一村民</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>穆伊斯卡</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>升时代黄金-50%</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>穆伊斯卡</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>聚落成本-33%且治疗附近</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>保加利亚</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>保加利亚</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>TC石料费用-50%</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>匈奴</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>无神论（敌方圣物产资源-50%；奇观/圣物胜利倒计时+100年）</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>瞿折罗</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>刹帝利（军事单位食物-25%）</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E31"/>
+  <autoFilter ref="A1:E83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -6419,7 +6635,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="51" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -6440,12 +6656,12 @@
       </c>
       <c r="E2" s="10" t="inlineStr">
         <is>
-          <t>初始村民+3，木材-50，食物-200；TC视野+7，人口+15；火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
+          <t>火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 4 / 弱 0）；经济科技树 16/18；缺 轮作、行会；最直接一条：初始村民+3，木材-50，食物-200</t>
+          <t>阶段1·本体强化；原生条目 8 条（强 4 / 弱 0）；经济科技树 16/18；缺 轮作、行会；最直接一条：初始村民+3，木材-50，食物-200</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6691,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：独轮推车/手推车免费</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：独轮推车/手推车免费</t>
         </is>
       </c>
     </row>
@@ -6505,7 +6721,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 4 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：采石村民缓慢获食</t>
+          <t>阶段1·本体强化；原生条目 8 条（强 4 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：采石村民缓慢获食</t>
         </is>
       </c>
     </row>
@@ -6530,16 +6746,16 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>石矿工速度+20%；远程/步兵木材费用-50%；战船木材-20%</t>
+          <t>石矿工速度+20%；神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）；战船木材-20%</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 5 条（强 3 / 弱 0）；经济科技树 17/18；缺 轮作；最直接一条：石矿工速度+20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 8 条（强 3 / 弱 0）；经济科技树 17/18；缺 轮作；最直接一条：石矿工速度+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -6560,12 +6776,12 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>可提前一个时代经济升级且食物-40%；勃艮第葡萄园（农民产食并缓慢产金）；弗拉芒革命（所有村民变弗拉芒民兵）</t>
+          <t>可提前一个时代经济升级且食物-40%；圣物不仅能产生黄金，还能产生食物</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 2 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：勃艮第葡萄园（农民产食并缓慢产金）</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：勃艮第葡萄园（农民产食并缓慢产金）</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6811,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3 / 弱 0）；经济科技树 17/18；缺 采石场；最直接一条：升时代TC产生2村民</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；经济科技树 17/18；缺 采石场；最直接一条：升时代TC产生2村民</t>
         </is>
       </c>
     </row>
@@ -6620,12 +6836,12 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>房屋/聚落人口+5；建筑石料-15%；军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%</t>
+          <t>建筑石料-15%；军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 2 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：房屋/聚落人口+5</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：房屋/聚落人口+5</t>
         </is>
       </c>
     </row>
@@ -6650,16 +6866,16 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>铁匠铺/大学木材费用-100；狂热/圣洁影响村民；胡斯革新（僧侣和修道院科技消耗黄金而非食物）</t>
+          <t>胡斯革新（僧侣和修道院科技消耗黄金而非食物）</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 5 条（强 2 / 弱 1）；经济科技树 17/18；缺 轮作；最直接一条：狂热/圣洁影响村民</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 7 条（强 2 / 弱 1）；经济科技树 17/18；缺 轮作；最直接一条：狂热/圣洁影响村民</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="51" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -6680,12 +6896,12 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>村民封建/城堡/帝王每分钟恢复10/15/20生命；石矿工产石料+黄金；血统/斥候食物费用-50%</t>
+          <t>石矿工产石料+黄金</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 5 条（强 2 / 弱 1）；经济科技树 15/18；缺 双人锯、钻井采金法、行会；最直接一条：村民封建/城堡/帝王每分钟恢复10/15/20生命</t>
+          <t>阶段1·本体强化；原生条目 7 条（强 2 / 弱 1）；经济科技树 15/18；缺 双人锯、钻井采金法、行会；最直接一条：村民封建/城堡/帝王每分钟恢复10/15/20生命</t>
         </is>
       </c>
     </row>
@@ -6710,12 +6926,12 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>开局每种资源+25；村民可驻聚落；靶场/兵营升级食物-50%</t>
+          <t>靶场/兵营升级食物-50%</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、行会；最直接一条：村民可驻聚落</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、行会；最直接一条：村民可驻聚落</t>
         </is>
       </c>
     </row>
@@ -6740,12 +6956,12 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>研究科技获黄金+20；霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）；贸易单位产生的黄金 +25%</t>
+          <t>研究科技获黄金+20</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、钻井采金法；最直接一条：霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、钻井采金法；最直接一条：霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）</t>
         </is>
       </c>
     </row>
@@ -6770,16 +6986,16 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>村民/捕鱼船存食+10%；希洛人征兵（长矛/掷矛/村民训练+50%）</t>
+          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：村民/捕鱼船存食+10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：村民/捕鱼船存食+10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -6800,12 +7016,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>农民工作速度+15%；罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）；军事建筑 (城堡除外) 提供的人口空间 +5</t>
+          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：农民工作速度+15%</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：农民工作速度+15%</t>
         </is>
       </c>
     </row>
@@ -6835,7 +7051,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：农民无需磨坊/TC即可存食</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：农民无需磨坊/TC即可存食</t>
         </is>
       </c>
     </row>
@@ -6860,12 +7076,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>村民黑暗/封建/城堡/帝王费用-8/13/18/23%；大干道（所有黄金收入速度+10%；市场交易费降至10%）</t>
+          <t>村民黑暗/封建/城堡/帝王费用-8/13/18/23%</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、行会；最直接一条：村民黑暗/封建/城堡/帝王费用-8/13/18/23%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、行会；最直接一条：村民黑暗/封建/城堡/帝王费用-8/13/18/23%</t>
         </is>
       </c>
     </row>
@@ -6895,11 +7111,11 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：猎人携带+15，猎物持续+20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：猎人携带+15，猎物持续+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="51" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -6925,7 +7141,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、双人锯；最直接一条：堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、双人锯；最直接一条：堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
         </is>
       </c>
     </row>
@@ -6955,7 +7171,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、双人锯、行会；最直接一条：猎人速度+40%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、双人锯、行会；最直接一条：猎人速度+40%</t>
         </is>
       </c>
     </row>
@@ -6985,7 +7201,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、行会；最直接一条：市场贸易税仅5%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、行会；最直接一条：市场贸易税仅5%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7226,12 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>渔夫/捕鱼船携带+15；升时代木材+200；攻城武器木材-33%</t>
+          <t>升时代木材+200；攻城武器木材-33%</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 1 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、钻井采金法；最直接一条：码头提供的人口空间 +5</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 1 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、钻井采金法；最直接一条：码头提供的人口空间 +5</t>
         </is>
       </c>
     </row>
@@ -7045,7 +7261,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；经济科技树 16/18；缺 双人锯、钻井采金法；最直接一条：强化教堂使9格内村民效率+10%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 双人锯、钻井采金法；最直接一条：强化教堂使9格内村民效率+10%</t>
         </is>
       </c>
     </row>
@@ -7070,12 +7286,12 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>初始黄金+50；村民携带量+3；圣物产生的黄金 +33%</t>
+          <t>初始黄金+50；圣物产生的黄金 +33%</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：村民携带量+3</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：村民携带量+3</t>
         </is>
       </c>
     </row>
@@ -7105,7 +7321,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：采果工存食+25%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：采果工存食+25%</t>
         </is>
       </c>
     </row>
@@ -7130,12 +7346,12 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>捕鱼船/村民存食+5%；摧毁建筑抢25%资源；兵营/攻城武器厂黄金升级-66%</t>
+          <t>兵营/攻城武器厂黄金升级-66%</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 0）；经济科技树 15/18；缺 轮作、双人锯、行会；最直接一条：捕鱼船/村民存食+5%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 0）；经济科技树 15/18；缺 轮作、双人锯、行会；最直接一条：捕鱼船/村民存食+5%</t>
         </is>
       </c>
     </row>
@@ -7160,12 +7376,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>伐木工缓慢产食；军役税（希腊步兵黄金50%改为额外食物）</t>
+          <t>军役税（希腊步兵黄金50%改为额外食物）；TC可切换政策风格（经济/海军/军事）</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 1）；经济科技树 18/18（无缺项）；最直接一条：伐木工缓慢产食</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 1）；经济科技树 18/18（无缺项）；最直接一条：伐木工缓慢产食</t>
         </is>
       </c>
     </row>
@@ -7190,12 +7406,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>攻城/防御工事升级木材-75%，研究+100%；霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）；攻城/防御工事升级木材-75%，研究+100%</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
         </is>
       </c>
     </row>
@@ -7220,12 +7436,12 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>建筑木材-15%；村民存金+10%</t>
+          <t>建筑木材-15%</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：村民存金+10%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：村民存金+10%</t>
         </is>
       </c>
     </row>
@@ -7255,7 +7471,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：开局村民+1，食物-50</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：开局村民+1，食物-50</t>
         </is>
       </c>
     </row>
@@ -7280,12 +7496,12 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>采果工产食+木材；所有单位黄金费用-20%</t>
+          <t>采果工产食+木材</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：采果工产食+木材</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：采果工产食+木材</t>
         </is>
       </c>
     </row>
@@ -7310,12 +7526,12 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>初始石料+100；农田升级食物+125%</t>
+          <t>初始石料+100</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：农田升级食物+125%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：农田升级食物+125%</t>
         </is>
       </c>
     </row>
@@ -7340,12 +7556,12 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>经济升级无木材且研究+100%；纸币（伐木工产木并缓慢产金）</t>
+          <t>经济升级无木材且研究+100%</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：纸币（伐木工产木并缓慢产金）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：纸币（伐木工产木并缓慢产金）</t>
         </is>
       </c>
     </row>
@@ -7370,12 +7586,12 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>羊倌工作速度+25%；城堡起TC木材费用-50%</t>
+          <t>城堡起TC木材费用-50%</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：羊倌工作速度+25%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：羊倌工作速度+25%</t>
         </is>
       </c>
     </row>
@@ -7400,12 +7616,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>村民收集/建造/修理速度+5%；蝎式弩黄金-50%</t>
+          <t>蝎式弩黄金-50%</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、采石场；最直接一条：村民收集/建造/修理速度+5%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、采石场；最直接一条：村民收集/建造/修理速度+5%</t>
         </is>
       </c>
     </row>
@@ -7430,12 +7646,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>养鱼场费用-33%且食物+200%；强征兵役（生产民兵系消耗额外食物而非黄金）</t>
+          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：养鱼场费用-33%且食物+200%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：养鱼场费用-33%且食物+200%</t>
         </is>
       </c>
     </row>
@@ -7460,12 +7676,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>村民一击杀狼；科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：村民一击杀狼</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：村民一击杀狼</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7711,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 1）；经济科技树 15/18；缺 双人锯、采石场、行会；最直接一条：采果工速度+15%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 1）；经济科技树 15/18；缺 双人锯、采石场、行会；最直接一条：采果工速度+15%</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7741,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：村民黑暗移速+5%，封建起+10%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：村民黑暗移速+5%，封建起+10%</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7771,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：农田费用-40%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：农田费用-40%</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7801,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：丝绸之路（贸易单位费用-50%）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：丝绸之路（贸易单位费用-50%）</t>
         </is>
       </c>
     </row>
@@ -7615,7 +7831,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、双人锯；最直接一条：伐木工速度+15%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、双人锯；最直接一条：伐木工速度+15%</t>
         </is>
       </c>
     </row>
@@ -7645,7 +7861,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：伐木工产木+食物</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：伐木工产木+食物</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7891,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：金矿工速度+25%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：金矿工速度+25%</t>
         </is>
       </c>
     </row>
@@ -7705,7 +7921,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：每研究一次经济升级免费获一村民</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：每研究一次经济升级免费获一村民</t>
         </is>
       </c>
     </row>
@@ -7730,12 +7946,12 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>升时代黄金-50%；聚落成本-33%且治疗附近；天然黄金资源持续时间 +15%</t>
+          <t>升时代黄金-50%；篷车/行会免费</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 0 / 弱 1）；经济科技树 18/18（无缺项）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 0 / 弱 1）；经济科技树 18/18（无缺项）</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7981,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；经济科技树 14/18；缺 重犁、重犁升级、轮作、钻井采金法；最直接一条：牧场取代农田</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 14/18；缺 重犁、重犁升级、轮作、钻井采金法；最直接一条：牧场取代农田</t>
         </is>
       </c>
     </row>
@@ -7795,7 +8011,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 0）；经济科技树 18/18（无缺项）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 18/18（无缺项）</t>
         </is>
       </c>
     </row>
@@ -7825,7 +8041,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 0）；经济科技树 17/18；缺 轮作</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 17/18；缺 轮作</t>
         </is>
       </c>
     </row>
@@ -7855,7 +8071,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 0）；经济科技树 17/18；缺 双人锯</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 17/18；缺 双人锯</t>
         </is>
       </c>
     </row>
@@ -7880,16 +8096,16 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>不需要房屋，但初始木材-100；无神论（敌方圣物产资源-50%；奇观/圣物胜利倒计时+100年）</t>
+          <t>不需要房屋，但初始木材-100</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 0）；经济科技树 16/18；缺 轮作、采石场</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 16/18；缺 轮作、采石场</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
@@ -7915,11 +8131,11 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 采石场</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 采石场</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
@@ -7945,11 +8161,11 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 钻井采金法</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 钻井采金法</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
@@ -7975,11 +8191,11 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 采石场</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 采石场</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
@@ -8005,11 +8221,11 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 钻井采金法</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 钻井采金法</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
@@ -8035,11 +8251,11 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 轮作</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 轮作</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
@@ -8065,11 +8281,11 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 1）；经济科技树 16/18；缺 双人锯、行会</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 1）；经济科技树 16/18；缺 双人锯、行会</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="36" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
@@ -8095,11 +8311,11 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；经济科技树 17/18；缺 采石场</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="28" customHeight="1">
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；经济科技树 17/18；缺 采石场</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="36" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
@@ -8125,7 +8341,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；经济科技树 16/18；缺 轮作、采石场</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；经济科技树 16/18；缺 轮作、采石场</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8435,101 +8651,141 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>① 只看直接作用于经济本体、或其前置/费用/产出的条目；</t>
+          <t>本表按用户打法口径分四个阶段排序：先加强要玩的主流派兵种，再减它的资源消耗，最后才补资源效率。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>① 阶段 1 · 本体强化</t>
+        </is>
+      </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>② 泛用条目与兵种类一律剔除（放进「与发育经济流无关·可跳过」）；</t>
+          <t>直接加强经济本体的条目（攻击/护甲/生命/攻速/射程/移速/回血/数量/生产训练速度/解锁升级等）。这一档最优先。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="12" t="inlineStr"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>② 阶段 2 · 减费用</t>
+        </is>
+      </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>③ 门槛越低、替代成本越高，名次越靠前。</t>
+          <t>降低该兵种及同系兵种（村民与采集生产）生产所需资源的条目：费用/成本 -N%、升级免费、用其它资源替代。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="12" t="inlineStr"/>
-      <c r="B17" s="12" t="inlineStr"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>③ 阶段 3 · 资源效率</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>采集/产出/携带/贸易/人口/经济科技等让主流派更快成型的条目。</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>未验证项</t>
+          <t>④ 阶段 4 · 其他相关</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
+          <t>其余与本流派相关、但不属于上述三类的条目。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>★ 最重要的一条：别买重复</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
+          <t>同阶段内按「人工权威顺序（实战强度）」再排；泛用条目与兵种类一律剔除（放进「与发育经济流无关·可跳过」）。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="12" t="inlineStr"/>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
-        </is>
-      </c>
+      <c r="B20" s="12" t="inlineStr"/>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>数据来源</t>
+          <t>未验证项</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="12" t="inlineStr"/>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>★ 最重要的一条：别买重复</t>
+        </is>
+      </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>整理</t>
-        </is>
-      </c>
+      <c r="A23" s="12" t="inlineStr"/>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>By RemonBo；本表由 DSH 生成。</t>
+          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="12" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>整理</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>By RemonBo；本表由 DSH 生成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
           <t>与本表配套</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>同目录下的箭塔流、炮塔流与其余流派总表。</t>
         </is>

--- a/帝国时代2决定版 文明联盟 发育经济流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 发育经济流最优研究顺序 By RemonBo.xlsx
@@ -20,9 +20,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$55</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·经济本体强化'!$A$1:$E$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·经济本体强化'!$A$1:$E$83</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·经济本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与发育经济流无关·可跳过'!$A$1:$D$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与发育经济流无关·可跳过'!$1:$1</definedName>
@@ -587,7 +587,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
+          <t>火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）；农田的食物 +10%；TC视野+7，人口+15</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -600,13 +600,13 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>高丽（备选）</t>
+          <t>勃艮第（备选）</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 8 条（强 3 / 弱 0）；经济科技树 17/18；缺 轮作；最直接一条：石矿工速度+20%</t>
+          <t>备选：阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：勃艮第葡萄园（农民产食并缓慢产金）</t>
         </is>
       </c>
     </row>
@@ -614,13 +614,13 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>勃艮第（备选）</t>
+          <t>孟加拉（备选）</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：勃艮第葡萄园（农民产食并缓慢产金）</t>
+          <t>备选：阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；经济科技树 17/18；缺 采石场；最直接一条：升时代TC产生2村民</t>
         </is>
       </c>
     </row>
@@ -638,17 +638,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>维京（首选）</t>
+          <t>普鲁人（首选）</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>独轮推车/手推车免费</t>
+          <t>采石村民缓慢获食；村民/捕鱼船采牡蛎+15%；吠陀教义（翰林院每项科技使村民效率+2%，最大20%）</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：独轮推车/手推车免费</t>
+          <t>阶段1·本体强化；原生条目 8 条（强 4 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：采石村民缓慢获食</t>
         </is>
       </c>
     </row>
@@ -656,13 +656,13 @@
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>孟加拉（备选）</t>
+          <t>印加（备选）</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；经济科技树 17/18；缺 采石场；最直接一条：升时代TC产生2村民</t>
+          <t>备选：阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：房屋/聚落人口+5</t>
         </is>
       </c>
     </row>
@@ -670,13 +670,13 @@
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>印加（备选）</t>
+          <t>波希米亚（备选）</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：房屋/聚落人口+5</t>
+          <t>备选：阶段1·本体强化；原生条目 7 条（强 2 / 弱 1）；经济科技树 17/18；缺 轮作；最直接一条：狂热/圣洁影响村民</t>
         </is>
       </c>
     </row>
@@ -694,45 +694,45 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>普鲁人（首选）</t>
+          <t>高丽（首选）</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>采石村民缓慢获食；村民/捕鱼船采牡蛎+15%；吠陀教义（翰林院每项科技使村民效率+2%，最大20%）</t>
+          <t>石矿工速度+20%；神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）；村民视野 +3</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 8 条（强 4 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：采石村民缓慢获食</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 8 条（强 3 / 弱 0）；经济科技树 17/18；缺 轮作；最直接一条：石矿工速度+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="51" customHeight="1">
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>波希米亚（备选）</t>
+          <t>波兰（备选）</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 7 条（强 2 / 弱 1）；经济科技树 17/18；缺 轮作；最直接一条：狂热/圣洁影响村民</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="51" customHeight="1">
+          <t>备选：阶段1·本体强化；原生条目 7 条（强 2 / 弱 1）；经济科技树 15/18；缺 双人锯、钻井采金法、行会；最直接一条：村民封建/城堡/帝王每分钟恢复10/15/20生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>波兰（备选）</t>
+          <t>图皮（备选）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 7 条（强 2 / 弱 1）；经济科技树 15/18；缺 双人锯、钻井采金法、行会；最直接一条：村民封建/城堡/帝王每分钟恢复10/15/20生命</t>
+          <t>备选：阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、行会；最直接一条：村民可驻聚落</t>
         </is>
       </c>
     </row>
@@ -797,13 +797,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="51" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>石矿工速度+20%；神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）；战船木材-20%</t>
+          <t>勃艮第葡萄园（农民产食并缓慢产金）；弗拉芒革命（所有村民变弗拉芒民兵）；圣物不仅能产生黄金，还能产生食物</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 8 条（强 3 / 弱 0）；经济科技树 17/18；缺 轮作；最直接一条：石矿工速度+20%</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：勃艮第葡萄园（农民产食并缓慢产金）</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>可提前一个时代经济升级且食物-40%；圣物不仅能产生黄金，还能产生食物</t>
+          <t>升时代TC产生2村民；贸易单位不仅能产生黄金，还能额外产生 10% 的食物</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -853,17 +853,17 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：勃艮第葡萄园（农民产食并缓慢产金）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；经济科技树 17/18；缺 采石场；最直接一条：升时代TC产生2村民</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -873,17 +873,17 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>升时代TC产生2村民；大乘佛教（村民/僧侣人口-10%）；贸易单位不仅能产生黄金，还能额外产生 10% 的食物</t>
+          <t>城堡起步兵铁匠铺升级影响村民；房屋/聚落人口+5</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>黑暗时代起</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；经济科技树 17/18；缺 采石场；最直接一条：升时代TC产生2村民</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：房屋/聚落人口+5</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -903,27 +903,27 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>建筑石料-15%；军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%</t>
+          <t>狂热/圣洁影响村民；市场效率 +80%</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>黑暗时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：房屋/聚落人口+5</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 7 条（强 2 / 弱 1）；经济科技树 17/18；缺 轮作；最直接一条：狂热/圣洁影响村民</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="51" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -933,27 +933,27 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>胡斯革新（僧侣和修道院科技消耗黄金而非食物）</t>
+          <t>村民封建/城堡/帝王每分钟恢复10/15/20生命；石矿工产石料+黄金</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>封建时代起</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 7 条（强 2 / 弱 1）；经济科技树 17/18；缺 轮作；最直接一条：狂热/圣洁影响村民</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 7 条（强 2 / 弱 1）；经济科技树 15/18；缺 双人锯、钻井采金法、行会；最直接一条：村民封建/城堡/帝王每分钟恢复10/15/20生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -963,27 +963,27 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>石矿工产石料+黄金</t>
+          <t>村民可驻聚落；塔楼和城堡提供的人口空间 +10；开局每种资源+25</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>封建时代起</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 7 条（强 2 / 弱 1）；经济科技树 15/18；缺 双人锯、钻井采金法、行会；最直接一条：村民封建/城堡/帝王每分钟恢复10/15/20生命</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、行会；最直接一条：村民可驻聚落</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="51" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -993,27 +993,27 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>靶场/兵营升级食物-50%</t>
+          <t>霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）；贸易单位产生的黄金 +25%；研究科技获黄金+20</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、行会；最直接一条：村民可驻聚落</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、钻井采金法；最直接一条：霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>研究科技获黄金+20</t>
+          <t>村民/捕鱼船存食+10%；希洛人征兵（长矛/掷矛/村民训练+50%）</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、钻井采金法；最直接一条：霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：村民/捕鱼船存食+10%</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
+          <t>农民工作速度+15%；军事建筑 (城堡除外) 提供的人口空间 +5</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：村民/捕鱼船存食+10%</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：农民工作速度+15%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>高棉</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1083,17 +1083,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
+          <t>农民无需磨坊/TC即可存食；村民可驻房</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：农民工作速度+15%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：农民无需磨坊/TC即可存食</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>农民无需磨坊/TC即可存食；村民可驻房</t>
+          <t>大干道（所有黄金收入速度+10%；市场交易费降至10%）</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>黑暗时代起</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：农民无需磨坊/TC即可存食</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、行会；最直接一条：村民黑暗/封建/城堡/帝王费用-8/13/18/23%</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1143,27 +1143,27 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>村民黑暗/封建/城堡/帝王费用-8/13/18/23%</t>
+          <t>猎人携带+15，猎物持续+20%；帝王人口+10</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>黑暗时代起</t>
+          <t>帝王时代起</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、行会；最直接一条：村民黑暗/封建/城堡/帝王费用-8/13/18/23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：猎人携带+15，猎物持续+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="51" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1173,27 +1173,27 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>猎人携带+15，猎物持续+20%；帝王人口+10</t>
+          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点；羊倌/猎人采食时缓慢产金</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>帝王时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：猎人携带+15，猎物持续+20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、双人锯；最直接一条：堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点；羊倌/猎人采食时缓慢产金</t>
+          <t>猎人速度+40%；游牧（失去房屋时人口不减）</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、双人锯；最直接一条：堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、双人锯、行会；最直接一条：猎人速度+40%</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>猎人速度+40%；游牧（失去房屋时人口不减）</t>
+          <t>市场贸易税仅5%</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、双人锯、行会；最直接一条：猎人速度+40%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、行会；最直接一条：市场贸易税仅5%</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>市场贸易税仅5%；市场木材-100</t>
+          <t>码头提供的人口空间 +5；渔夫/捕鱼船携带+15；升时代木材+200</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1273,17 +1273,17 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、行会；最直接一条：市场贸易税仅5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 1 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、钻井采金法；最直接一条：码头提供的人口空间 +5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="51" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>升时代木材+200；攻城武器木材-33%</t>
+          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 1 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、钻井采金法；最直接一条：码头提供的人口空间 +5</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>强化教堂使9格内村民效率+10%；阿兹瑙里骑兵（骑兵人口-20%）</t>
+          <t>农田升级食物+125%；初始石料+100</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 双人锯、钻井采金法；最直接一条：强化教堂使9格内村民效率+10%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：农田升级食物+125%</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1353,17 +1353,17 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>初始黄金+50；圣物产生的黄金 +33%</t>
+          <t>羊倌工作速度+25%</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：村民携带量+3</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：羊倌工作速度+25%</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1383,17 +1383,17 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>采果工存食+25%；聚落可训长矛/掷矛；骑兵杀敌+3黄金</t>
+          <t>村民黑暗移速+5%，封建起+10%</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>黑暗时代起</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：采果工存食+25%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：村民黑暗移速+5%，封建起+10%</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>兵营/攻城武器厂黄金升级-66%</t>
+          <t>捕鱼船/村民存食+5%；摧毁建筑抢25%资源</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>雅典</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>军役税（希腊步兵黄金50%改为额外食物）；TC可切换政策风格（经济/海军/军事）</t>
+          <t>牧场取代农田</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -1453,17 +1453,17 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 1）；经济科技树 18/18（无缺项）；最直接一条：伐木工缓慢产食</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 14/18；缺 重犁、重犁升级、轮作、钻井采金法；最直接一条：牧场取代农田</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）；攻城/防御工事升级木材-75%，研究+100%</t>
+          <t>纸币（伐木工产木并缓慢产金）；经济升级无木材且研究+100%</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：纸币（伐木工产木并缓慢产金）</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>建筑木材-15%</t>
+          <t>村民携带量+3；初始黄金+50；圣物产生的黄金 +33%</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：村民存金+10%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：村民携带量+3</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>开局村民+1，食物-50；资源持续+15%</t>
+          <t>强化教堂使9格内村民效率+10%</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：开局村民+1，食物-50</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 双人锯、钻井采金法；最直接一条：强化教堂使9格内村民效率+10%</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>采果工产食+木材</t>
+          <t>采果工存食+25%；聚落可训长矛/掷矛；骑兵杀敌+3黄金</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：采果工产食+木材</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：采果工存食+25%</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>初始石料+100</t>
+          <t>采果工速度+15%</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：农田升级食物+125%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 1）；经济科技树 15/18；缺 双人锯、采石场、行会；最直接一条：采果工速度+15%</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>经济升级无木材且研究+100%</t>
+          <t>伐木工缓慢产食；军役税（希腊步兵黄金50%改为额外食物）</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：纸币（伐木工产木并缓慢产金）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 1）；经济科技树 18/18（无缺项）；最直接一条：伐木工缓慢产食</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>穆伊斯卡</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>城堡起TC木材费用-50%</t>
+          <t>天然黄金资源持续时间 +15%</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：羊倌工作速度+25%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 0 / 弱 1）；经济科技树 18/18（无缺项）</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>蝎式弩黄金-50%</t>
+          <t>村民存金+10%</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、采石场；最直接一条：村民收集/建造/修理速度+5%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：村民存金+10%</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
+          <t>资源持续+15%</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：养鱼场费用-33%且食物+200%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：开局村民+1，食物-50</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+          <t>采果工产食+木材</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：村民一击杀狼</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：采果工产食+木材</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>采果工速度+15%；王家敕令骑兵（骑马弩手黄金-40%）</t>
+          <t>村民收集/建造/修理速度+5%</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 1）；经济科技树 15/18；缺 双人锯、采石场、行会；最直接一条：采果工速度+15%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、采石场；最直接一条：村民收集/建造/修理速度+5%</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -1803,17 +1803,17 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>村民黑暗移速+5%，封建起+10%</t>
+          <t>村民一击杀狼</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>黑暗时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：村民黑暗移速+5%，封建起+10%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：村民一击杀狼</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>农田费用-40%</t>
+          <t>伐木工速度+15%</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：农田费用-40%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、双人锯；最直接一条：伐木工速度+15%</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>丝绸之路（贸易单位费用-50%）</t>
+          <t>伐木工产木+食物</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：丝绸之路（贸易单位费用-50%）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：伐木工产木+食物</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>伐木工速度+15%</t>
+          <t>金矿工速度+25%</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、双人锯；最直接一条：伐木工速度+15%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：金矿工速度+25%</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>伐木工产木+食物</t>
+          <t>初始木材/食物+50</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：伐木工产木+食物</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 18/18（无缺项）</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>金矿工速度+25%</t>
+          <t>升时代获得黄金+100、食物+100；哨站视野 +3 且不消耗石料</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：金矿工速度+25%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 17/18；缺 轮作</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>每研究一次经济升级免费获一村民</t>
+          <t>牲畜驻磨坊被动产食</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：每研究一次经济升级免费获一村民</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 1）；经济科技树 16/18；缺 双人锯、行会</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>升时代黄金-50%；篷车/行会免费</t>
+          <t>不需要房屋，但初始木材-100</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 0 / 弱 1）；经济科技树 18/18（无缺项）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 16/18；缺 轮作、采石场</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>牧场取代农田</t>
+          <t>每座TC食物+100</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 14/18；缺 重犁、重犁升级、轮作、钻井采金法；最直接一条：牧场取代农田</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 钻井采金法</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>初始木材/食物+50；波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
+          <t>磨坊/木料/采矿场建成后食物+35，石料+10</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 18/18（无缺项）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 采石场</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>升时代获得黄金+100、食物+100；哨站视野 +3 且不消耗石料</t>
+          <t>牧羊/捕鱼/狩猎也产黄金</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 17/18；缺 轮作</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 钻井采金法</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>铁匠铺/攻城武器厂科技食物费用-50%；TC石料费用-50%</t>
+          <t>军事建筑/码头建成后食物+55</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 17/18；缺 双人锯</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 轮作</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>不需要房屋，但初始木材-100</t>
+          <t>每研究一次经济升级免费获一村民</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 16/18；缺 轮作、采石场</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：每研究一次经济升级免费获一村民</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>靶场/马厩木材-75</t>
+          <t>养鱼场费用-33%且食物+200%；强征兵役（生产民兵系消耗额外食物而非黄金）</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 采石场</t>
+          <t>阶段2·减费用；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：养鱼场费用-33%且食物+200%</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>每座TC食物+100</t>
+          <t>靶场/马厩木材-75</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 钻井采金法</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 采石场</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>磨坊/木料/采矿场建成后食物+35，石料+10</t>
+          <t>独轮推车/手推车免费</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 采石场</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：独轮推车/手推车免费</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>牧羊/捕鱼/狩猎也产黄金</t>
+          <t>铁匠铺/攻城武器厂科技食物费用-50%；TC石料费用-50%</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 钻井采金法</t>
+          <t>阶段2·减费用；原生条目 2 条（强 0 / 弱 0）；经济科技树 17/18；缺 双人锯</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>军事建筑/码头建成后食物+55</t>
+          <t>伐木场科技免费</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 轮作</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；经济科技树 17/18；缺 采石场</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>刹帝利（军事单位食物-25%）</t>
+          <t>农田费用-40%</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 1）；经济科技树 16/18；缺 双人锯、行会</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：农田费用-40%</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>伐木场科技免费</t>
+          <t>丝绸之路（贸易单位费用-50%）</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；经济科技树 17/18；缺 采石场</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：丝绸之路（贸易单位费用-50%）</t>
         </is>
       </c>
     </row>
@@ -2425,1325 +2425,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E48"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>档</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>文明</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>条目原文</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>作用说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>中国</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>高丽</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>石矿工速度+20%</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>工作速度提升，成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>高丽</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>射程提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>高丽</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>战船木材-20%</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>勃艮第</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>可提前一个时代经济升级且食物-40%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>提前解锁，抢一个时代的节奏</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>勃艮第</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>圣物不仅能产生黄金，还能产生食物</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>建筑石料-15%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>胡斯革新（僧侣和修道院科技消耗黄金而非食物）</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>石矿工产石料+黄金</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>额外产出资源，经济滚雪球更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>靶场/兵营升级食物-50%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>西班牙</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>研究科技获黄金+20</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>训练速度提升，成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>达罗毗荼</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>升时代木材+200</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>达罗毗荼</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>攻城武器木材-33%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>初始黄金+50</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>圣物产生的黄金 +33%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>马普切</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>采果工存食+25%</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>马普切</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>聚落可训长矛/掷矛</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>马普切</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>骑兵杀敌+3黄金</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>兵营/攻城武器厂黄金升级-66%</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>军役税（希腊步兵黄金50%改为额外食物）</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>TC可切换政策风格（经济/海军/军事）</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>可切换政策风格，按局势临时调整</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>女真</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>爆炸/溅射范围提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>女真</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>攻城/防御工事升级木材-75%，研究+100%</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>马里</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>建筑木材-15%</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>葡萄牙</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>采果工产食+木材</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>西西里</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>初始石料+100</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>越南</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>经济升级无木材且研究+100%</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>蝎式弩黄金-50%</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>马来</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>马扎尔</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>法兰克</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>采果工速度+15%</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>法兰克</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>土耳其</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>金矿工速度+25%</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>工作速度提升，成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>穆伊斯卡</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>升时代黄金-50%</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>穆伊斯卡</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>篷车/行会免费</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>免费获得，等于直接省下这笔支出</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>初始木材/食物+50</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>升时代获得黄金+100、食物+100</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>哨站视野 +3 且不消耗石料</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>视野提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>匈奴</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>不需要房屋，但初始木材-100</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>库曼</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>靶场/马厩木材-75</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>立陶宛</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>每座TC食物+100</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>瓦兰吉人</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>牧羊/捕鱼/狩猎也产黄金</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>吴</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>军事建筑/码头建成后食物+55</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>瞿折罗</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>刹帝利（军事单位食物-25%）</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E48"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3799,7 +2480,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>初始村民+3，木材-50，食物-200</t>
+          <t>TC视野+7，人口+15</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -3809,7 +2490,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>资源产出/节省，加快成型</t>
+          <t>视野提升</t>
         </is>
       </c>
     </row>
@@ -3826,17 +2507,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>TC视野+7，人口+15</t>
+          <t>火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>视野提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -3875,12 +2556,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>独轮推车/手推车免费</t>
+          <t>采石村民缓慢获食</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -3890,7 +2571,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>免费获得，等于直接省下这笔支出</t>
+          <t>采集效率提升，经济成型更快</t>
         </is>
       </c>
     </row>
@@ -3907,7 +2588,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>采石村民缓慢获食</t>
+          <t>村民/捕鱼船采牡蛎+15%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -3934,12 +2615,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>村民/捕鱼船采牡蛎+15%</t>
+          <t>吠陀教义（翰林院每项科技使村民效率+2%，最大20%）</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -3961,17 +2642,17 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>吠陀教义（翰林院每项科技使村民效率+2%，最大20%）</t>
+          <t>贸易车移动速度 +15%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>采集效率提升，经济成型更快</t>
+          <t>机动性提升</t>
         </is>
       </c>
     </row>
@@ -3983,22 +2664,2286 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>贸易车移动速度 +15%</t>
+          <t>石矿工速度+20%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>射程提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>村民视野 +3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>团队加成</t>
         </is>
       </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>视野提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>勃艮第葡萄园（农民产食并缓慢产金）</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>额外产出资源，经济滚雪球更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>弗拉芒革命（所有村民变弗拉芒民兵）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>圣物不仅能产生黄金，还能产生食物</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>孟加拉</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>升时代TC产生2村民</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>额外获得村民，开局更宽裕</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>孟加拉</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>贸易单位不仅能产生黄金，还能额外产生 10% 的食物</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>市场/贸易收益提升，黄金来得更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>房屋/聚落人口+5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>人口容量提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>城堡起步兵铁匠铺升级影响村民</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>狂热/圣洁影响村民</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>市场效率 +80%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>村民封建/城堡/帝王每分钟恢复10/15/20生命</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>石矿工产石料+黄金</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>额外产出资源，经济滚雪球更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>村民可驻聚落</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>可驻扎，受攻击时更安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>塔楼和城堡提供的人口空间 +10</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>开局每种资源+25</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>贸易单位产生的黄金 +25%</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>市场/贸易收益提升，黄金来得更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>研究科技获黄金+20</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>斯巴达</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>村民/捕鱼船存食+10%</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>资源存放上限提升，少跑几趟</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>斯巴达</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>训练速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>斯拉夫</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>农民工作速度+15%</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>斯拉夫</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>军事建筑 (城堡除外) 提供的人口空间 +5</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>高棉</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>农民无需磨坊/TC即可存食</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>资源存放上限提升，少跑几趟</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>高棉</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>村民可驻房</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>可驻扎，受攻击时更安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>印度斯坦</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>大干道（所有黄金收入速度+10%；市场交易费降至10%）</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>市场/贸易收益提升，黄金来得更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>哥特</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>猎人携带+15，猎物持续+20%</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>携带量提升，往返次数更少</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>哥特</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>帝王人口+10</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>人口容量提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>羊倌/猎人采食时缓慢产金</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>额外产出资源，经济滚雪球更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>蒙古</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>猎人速度+40%</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>蒙古</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>游牧（失去房屋时人口不减）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>人口容量提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>萨拉森</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>市场贸易税仅5%</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>市场/贸易收益提升，黄金来得更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>码头提供的人口空间 +5</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>渔夫/捕鱼船携带+15</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>升时代木材+200</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>女真</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>爆炸/溅射范围提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>西西里</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>农田升级食物+125%</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>西西里</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>初始石料+100</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>不列颠</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>羊倌工作速度+25%</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>村民黑暗移速+5%，封建起+10%</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>捕鱼船/村民存食+5%</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>资源存放上限提升，少跑几趟</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>摧毁建筑抢25%资源</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>契丹</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>牧场取代农田</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>解锁升级形态，本流派的上限更高</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>纸币（伐木工产木并缓慢产金）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>经济升级无木材且研究+100%</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>阿兹特克</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>村民携带量+3</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>携带量提升，往返次数更少</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>阿兹特克</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>初始黄金+50</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>阿兹特克</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>圣物产生的黄金 +33%</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>格鲁吉亚</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>强化教堂使9格内村民效率+10%</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>采果工存食+25%</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="36" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>聚落可训长矛/掷矛</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>骑兵杀敌+3黄金</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>采果工速度+15%</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>雅典</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>伐木工缓慢产食</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>雅典</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>军役税（希腊步兵黄金50%改为额外食物）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>穆伊斯卡</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>天然黄金资源持续时间 +15%</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>马里</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>村民存金+10%</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>资源存放上限提升，少跑几趟</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>玛雅</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>资源持续+15%</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>采果工产食+木材</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>村民收集/建造/修理速度+5%</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>村民一击杀狼</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>一击必杀，反骚扰更省心</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>凯尔特</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>伐木工速度+15%</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>伐木工产木+食物</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>土耳其</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>金矿工速度+25%</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="28" customHeight="1">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>初始木材/食物+50</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>升时代获得黄金+100、食物+100</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="28" customHeight="1">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>哨站视野 +3 且不消耗石料</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>视野提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>瞿折罗</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>牲畜驻磨坊被动产食</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>额外产出资源，经济滚雪球更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>立陶宛</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>每座TC食物+100</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>撒克逊人</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>磨坊/木料/采矿场建成后食物+35，石料+10</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="28" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>瓦兰吉人</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>牧羊/捕鱼/狩猎也产黄金</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>采集效率提升，经济成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="28" customHeight="1">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>吴</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>军事建筑/码头建成后食物+55</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="36" customHeight="1">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>魏</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>每研究一次经济升级免费获一村民</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E83"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>档</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>文明</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>条目原文</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>作用说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>初始村民+3，木材-50，食物-200</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>远程/步兵木材费用-50%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>战船木材-20%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>可提前一个时代经济升级且食物-40%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>孟加拉</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>大乘佛教（村民/僧侣人口-10%）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>建筑石料-15%</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>铁匠铺/大学木材费用-100</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>机动性提升</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
@@ -4010,26 +4955,26 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>远程/步兵木材费用-50%</t>
+          <t>胡斯革新（僧侣和修道院科技消耗黄金而非食物）</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>A</t>
@@ -4037,22 +4982,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>村民视野 +3</t>
+          <t>采矿场科技免费</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>视野提升</t>
+          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
         </is>
       </c>
     </row>
@@ -4064,49 +5009,49 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>勃艮第葡萄园（农民产食并缓慢产金）</t>
+          <t>血统/斥候食物费用-50%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>贵族特权（骑士黄金费用-60%）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>额外产出资源，经济滚雪球更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>勃艮第</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>弗拉芒革命（所有村民变弗拉芒民兵）</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
@@ -4118,12 +5063,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>升时代TC产生2村民</t>
+          <t>大庄园替代磨坊</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4133,132 +5078,132 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>额外获得村民，开局更宽裕</t>
+          <t>直接强化经济</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>大乘佛教（村民/僧侣人口-10%）</t>
+          <t>靶场/兵营升级食物-50%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>斯拉夫</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>印度斯坦</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>村民黑暗/封建/城堡/帝王费用-8/13/18/23%</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>孟加拉</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>贸易单位不仅能产生黄金，还能额外产生 10% 的食物</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>萨拉森</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>市场木材-100</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>市场/贸易收益提升，黄金来得更快</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>房屋/聚落人口+5</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>人口容量提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>城堡起步兵铁匠铺升级影响村民</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
-        </is>
-      </c>
-    </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>铁匠铺/大学木材费用-100</t>
+          <t>攻城武器木材-33%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -4272,20 +5217,20 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>采矿场科技免费</t>
+          <t>攻城/防御工事升级木材-75%，研究+100%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4295,699 +5240,699 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>不列颠</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>城堡起TC木材费用-50%</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>兵营/攻城武器厂黄金升级-66%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>格鲁吉亚</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>阿兹瑙里骑兵（骑兵人口-20%）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>磨坊科技免费</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
           <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>狂热/圣洁影响村民</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>村民可吃该加成或转为战斗单位，后期更灵活</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>市场效率 +80%</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>血统/斥候食物费用-50%</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>穆伊斯卡</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>升时代黄金-50%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>贵族特权（骑士黄金费用-60%）</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>穆伊斯卡</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>聚落成本-33%且治疗附近</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>穆伊斯卡</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>篷车/行会免费</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>免费获得，等于直接省下这笔支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>马里</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>建筑木材-15%</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>玛雅</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>开局村民+1，食物-50</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>蝎式弩黄金-50%</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>瞿折罗</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>刹帝利（军事单位食物-25%）</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>村民封建/城堡/帝王每分钟恢复10/15/20生命</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>大庄园替代磨坊</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>直接强化经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>村民可驻聚落</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>可驻扎，受攻击时更安全</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>塔楼和城堡提供的人口空间 +10</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>开局每种资源+25</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>匈奴</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>不需要房屋，但初始木材-100</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>西班牙</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>马来</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>养鱼场费用-33%且食物+200%</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>马来</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>西班牙</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>贸易单位产生的黄金 +25%</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>市场/贸易收益提升，黄金来得更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>村民/捕鱼船存食+10%</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>资源存放上限提升，少跑几趟</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>斯拉夫</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>库曼</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>靶场/马厩木材-75</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>维京</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>独轮推车/手推车免费</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>免费获得，等于直接省下这笔支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>保加利亚</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>保加利亚</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>TC石料费用-50%</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>缅甸</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>伐木场科技免费</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>条顿</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>农田费用-40%</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>意大利</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>丝绸之路（贸易单位费用-50%）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>斯拉夫</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>农民工作速度+15%</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>工作速度提升，成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>斯拉夫</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>军事建筑 (城堡除外) 提供的人口空间 +5</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>高棉</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>农民无需磨坊/TC即可存食</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>资源存放上限提升，少跑几趟</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>高棉</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>村民可驻房</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>可驻扎，受攻击时更安全</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>印度斯坦</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>村民黑暗/封建/城堡/帝王费用-8/13/18/23%</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>印度斯坦</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>大干道（所有黄金收入速度+10%；市场交易费降至10%）</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>市场/贸易收益提升，黄金来得更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>哥特</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>猎人携带+15，猎物持续+20%</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>携带量提升，往返次数更少</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>哥特</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>帝王人口+10</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>人口容量提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>羊倌/猎人采食时缓慢产金</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>额外产出资源，经济滚雪球更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>蒙古</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>猎人速度+40%</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>工作速度提升，成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>蒙古</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>游牧（失去房屋时人口不减）</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>人口容量提升</t>
-        </is>
-      </c>
-    </row>
     <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>市场贸易税仅5%</t>
+          <t>磨坊/伐木场/采矿场费用-50%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -4997,1011 +5942,12 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>市场/贸易收益提升，黄金来得更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>萨拉森</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>市场木材-100</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>市场/贸易收益提升，黄金来得更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="36" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>达罗毗荼</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>码头提供的人口空间 +5</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>达罗毗荼</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>渔夫/捕鱼船携带+15</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>格鲁吉亚</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>强化教堂使9格内村民效率+10%</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>格鲁吉亚</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>阿兹瑙里骑兵（骑兵人口-20%）</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>村民携带量+3</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>携带量提升，往返次数更少</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>捕鱼船/村民存食+5%</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>资源存放上限提升，少跑几趟</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>摧毁建筑抢25%资源</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>伐木工缓慢产食</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>马里</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>村民存金+10%</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>资源存放上限提升，少跑几趟</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>玛雅</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>开局村民+1，食物-50</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>玛雅</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>资源持续+15%</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>葡萄牙</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>所有单位黄金费用-20%</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>西西里</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>农田升级食物+125%</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="28" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>越南</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>纸币（伐木工产木并缓慢产金）</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="28" customHeight="1">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>不列颠</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>城堡起TC木材费用-50%</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>不列颠</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>羊倌工作速度+25%</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>工作速度提升，成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>村民收集/建造/修理速度+5%</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>工作速度提升，成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>马来</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>养鱼场费用-33%且食物+200%</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>马扎尔</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>村民一击杀狼</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>一击必杀，反骚扰更省心</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="36" customHeight="1">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>法兰克</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>磨坊科技免费</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>柏柏尔</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>村民黑暗移速+5%，封建起+10%</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>机动性提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="28" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>条顿</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>农田费用-40%</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="28" customHeight="1">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>意大利</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>丝绸之路（贸易单位费用-50%）</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="28" customHeight="1">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>凯尔特</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>伐木工速度+15%</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="28" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>蜀</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>伐木工产木+食物</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="36" customHeight="1">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>魏</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>每研究一次经济升级免费获一村民</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="28" customHeight="1">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>穆伊斯卡</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>聚落成本-33%且治疗附近</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="28" customHeight="1">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>穆伊斯卡</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>天然黄金资源持续时间 +15%</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="28" customHeight="1">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>契丹</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>牧场取代农田</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>解锁升级形态，本流派的上限更高</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="28" customHeight="1">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>保加利亚</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="28" customHeight="1">
-      <c r="A78" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>保加利亚</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>TC石料费用-50%</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="28" customHeight="1">
-      <c r="A79" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>匈奴</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>无神论（敌方圣物产资源-50%；奇观/圣物胜利倒计时+100年）</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="28" customHeight="1">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>撒克逊人</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>磨坊/木料/采矿场建成后食物+35，石料+10</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>采集效率提升，经济成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="28" customHeight="1">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>瞿折罗</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>牲畜驻磨坊被动产食</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>额外产出资源，经济滚雪球更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="36" customHeight="1">
-      <c r="A82" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>缅甸</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>伐木场科技免费</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="28" customHeight="1">
-      <c r="A83" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>日本</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>磨坊/伐木场/采矿场费用-50%</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E83"/>
+  <autoFilter ref="A1:E46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -6235,32 +6181,32 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>独轮推车/手推车免费</t>
+          <t>采石村民缓慢获食；村民/捕鱼船采牡蛎+15%</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；经济科技树 16/18。缺：采石场、行会</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
+          <t>原生条目 4 条（强 4）；经济科技树 17/18。缺：钻井采金法</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -6270,12 +6216,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>采石村民缓慢获食；村民/捕鱼船采牡蛎+15%</t>
+          <t>石矿工速度+20%；神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 4）；经济科技树 17/18。缺：钻井采金法</t>
+          <t>原生条目 5 条（强 3）；经济科技树 17/18。缺：轮作</t>
         </is>
       </c>
     </row>
@@ -6285,47 +6231,47 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>石矿工速度+20%；神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）</t>
+          <t>勃艮第葡萄园（农民产食并缓慢产金）；弗拉芒革命（所有村民变弗拉芒民兵）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 5 条（强 3）；经济科技树 17/18。缺：轮作</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
+          <t>原生条目 4 条（强 2）；经济科技树 18/18。科技树无缺项</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>勃艮第葡萄园（农民产食并缓慢产金）；弗拉芒革命（所有村民变弗拉芒民兵）</t>
+          <t>升时代TC产生2村民；大乘佛教（村民/僧侣人口-10%）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 2）；经济科技树 18/18。科技树无缺项</t>
+          <t>原生条目 3 条（强 3）；经济科技树 17/18。缺：采石场</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6281,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -6345,12 +6291,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>升时代TC产生2村民；大乘佛教（村民/僧侣人口-10%）</t>
+          <t>房屋/聚落人口+5；城堡起步兵铁匠铺升级影响村民</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3）；经济科技树 17/18。缺：采石场</t>
+          <t>原生条目 4 条（强 2）；经济科技树 17/18。缺：双人锯</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6306,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -6370,47 +6316,47 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>房屋/聚落人口+5；城堡起步兵铁匠铺升级影响村民</t>
+          <t>狂热/圣洁影响村民；市场效率 +80%</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 2）；经济科技树 17/18。缺：双人锯</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
+          <t>原生条目 5 条（强 2）；经济科技树 17/18。缺：轮作</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>狂热/圣洁影响村民；市场效率 +80%</t>
+          <t>村民封建/城堡/帝王每分钟恢复10/15/20生命；石矿工产石料+黄金</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 5 条（强 2）；经济科技树 17/18。缺：轮作</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
+          <t>原生条目 5 条（强 2）；经济科技树 15/18。缺：双人锯、钻井采金法、行会</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -6420,37 +6366,37 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>村民封建/城堡/帝王每分钟恢复10/15/20生命；石矿工产石料+黄金</t>
+          <t>村民可驻聚落；塔楼和城堡提供的人口空间 +10</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 5 条（强 2）；经济科技树 15/18。缺：双人锯、钻井采金法、行会</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
+          <t>原生条目 4 条（强 2）；经济科技树 15/18。缺：轮作、采石场、行会</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>村民可驻聚落；塔楼和城堡提供的人口空间 +10</t>
+          <t>霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）；贸易单位产生的黄金 +25%</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 2）；经济科技树 15/18。缺：轮作、采石场、行会</t>
+          <t>原生条目 3 条（强 2）；经济科技树 16/18。缺：轮作、钻井采金法</t>
         </is>
       </c>
     </row>
@@ -6460,22 +6406,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）；贸易单位产生的黄金 +25%</t>
+          <t>村民/捕鱼船存食+10%；希洛人征兵（长矛/掷矛/村民训练+50%）</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2）；经济科技树 16/18。缺：轮作、钻井采金法</t>
+          <t>原生条目 2 条（强 2）；经济科技树 17/18。缺：钻井采金法</t>
         </is>
       </c>
     </row>
@@ -6485,32 +6431,32 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>村民/捕鱼船存食+10%；希洛人征兵（长矛/掷矛/村民训练+50%）</t>
+          <t>农民工作速度+15%；军事建筑 (城堡除外) 提供的人口空间 +5</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；经济科技树 17/18。缺：钻井采金法</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
+          <t>原生条目 3 条（强 2）；经济科技树 16/18。缺：采石场、行会</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>高棉</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -6520,22 +6466,22 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>农民工作速度+15%；军事建筑 (城堡除外) 提供的人口空间 +5</t>
+          <t>农民无需磨坊/TC即可存食；村民可驻房</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2）；经济科技树 16/18。缺：采石场、行会</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
+          <t>原生条目 2 条（强 2）；经济科技树 16/18。缺：双人锯、行会</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -6545,37 +6491,37 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>农民无需磨坊/TC即可存食；村民可驻房</t>
+          <t>村民黑暗/封建/城堡/帝王费用-8/13/18/23%；大干道（所有黄金收入速度+10%；市场交易费降至10%）</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；经济科技树 16/18。缺：双人锯、行会</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
+          <t>原生条目 2 条（强 2）；经济科技树 16/18。缺：轮作、行会</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>村民黑暗/封建/城堡/帝王费用-8/13/18/23%；大干道（所有黄金收入速度+10%；市场交易费降至10%）</t>
+          <t>猎人携带+15，猎物持续+20%；帝王人口+10</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；经济科技树 16/18。缺：轮作、行会</t>
+          <t>原生条目 2 条（强 2）；经济科技树 17/18。缺：钻井采金法</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6602,7 @@
       </c>
       <c r="E2" s="10" t="inlineStr">
         <is>
-          <t>火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
+          <t>火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）；农田的食物 +10%；TC视野+7，人口+15</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -6671,7 +6617,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -6686,12 +6632,12 @@
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>独轮推车/手推车免费</t>
+          <t>采石村民缓慢获食；村民/捕鱼船采牡蛎+15%；吠陀教义（翰林院每项科技使村民效率+2%，最大20%）</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：独轮推车/手推车免费</t>
+          <t>阶段1·本体强化；原生条目 8 条（强 4 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：采石村民缓慢获食</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6647,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -6716,22 +6662,22 @@
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>采石村民缓慢获食；村民/捕鱼船采牡蛎+15%；吠陀教义（翰林院每项科技使村民效率+2%，最大20%）</t>
+          <t>石矿工速度+20%；神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）；村民视野 +3</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 8 条（强 4 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：采石村民缓慢获食</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 8 条（强 3 / 弱 0）；经济科技树 17/18；缺 轮作；最直接一条：石矿工速度+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="51" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -6746,12 +6692,12 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>石矿工速度+20%；神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）；战船木材-20%</t>
+          <t>勃艮第葡萄园（农民产食并缓慢产金）；弗拉芒革命（所有村民变弗拉芒民兵）；圣物不仅能产生黄金，还能产生食物</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 8 条（强 3 / 弱 0）；经济科技树 17/18；缺 轮作；最直接一条：石矿工速度+20%</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：勃艮第葡萄园（农民产食并缓慢产金）</t>
         </is>
       </c>
     </row>
@@ -6761,7 +6707,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -6776,22 +6722,22 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>可提前一个时代经济升级且食物-40%；圣物不仅能产生黄金，还能产生食物</t>
+          <t>升时代TC产生2村民；贸易单位不仅能产生黄金，还能额外产生 10% 的食物</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：勃艮第葡萄园（农民产食并缓慢产金）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；经济科技树 17/18；缺 采石场；最直接一条：升时代TC产生2村民</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -6806,12 +6752,12 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>升时代TC产生2村民；大乘佛教（村民/僧侣人口-10%）；贸易单位不仅能产生黄金，还能额外产生 10% 的食物</t>
+          <t>城堡起步兵铁匠铺升级影响村民；房屋/聚落人口+5</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；经济科技树 17/18；缺 采石场；最直接一条：升时代TC产生2村民</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：房屋/聚落人口+5</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6767,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6836,22 +6782,22 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>建筑石料-15%；军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%</t>
+          <t>狂热/圣洁影响村民；市场效率 +80%</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：房屋/聚落人口+5</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 7 条（强 2 / 弱 1）；经济科技树 17/18；缺 轮作；最直接一条：狂热/圣洁影响村民</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="51" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6866,22 +6812,22 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>胡斯革新（僧侣和修道院科技消耗黄金而非食物）</t>
+          <t>村民封建/城堡/帝王每分钟恢复10/15/20生命；石矿工产石料+黄金</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 7 条（强 2 / 弱 1）；经济科技树 17/18；缺 轮作；最直接一条：狂热/圣洁影响村民</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 7 条（强 2 / 弱 1）；经济科技树 15/18；缺 双人锯、钻井采金法、行会；最直接一条：村民封建/城堡/帝王每分钟恢复10/15/20生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -6896,22 +6842,22 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>石矿工产石料+黄金</t>
+          <t>村民可驻聚落；塔楼和城堡提供的人口空间 +10；开局每种资源+25</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 7 条（强 2 / 弱 1）；经济科技树 15/18；缺 双人锯、钻井采金法、行会；最直接一条：村民封建/城堡/帝王每分钟恢复10/15/20生命</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、行会；最直接一条：村民可驻聚落</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="51" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -6926,22 +6872,22 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>靶场/兵营升级食物-50%</t>
+          <t>霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）；贸易单位产生的黄金 +25%；研究科技获黄金+20</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、行会；最直接一条：村民可驻聚落</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、钻井采金法；最直接一条：霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -6956,12 +6902,12 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>研究科技获黄金+20</t>
+          <t>村民/捕鱼船存食+10%；希洛人征兵（长矛/掷矛/村民训练+50%）</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、钻井采金法；最直接一条：霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：村民/捕鱼船存食+10%</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6917,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -6986,12 +6932,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
+          <t>农民工作速度+15%；军事建筑 (城堡除外) 提供的人口空间 +5</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：村民/捕鱼船存食+10%</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：农民工作速度+15%</t>
         </is>
       </c>
     </row>
@@ -7001,7 +6947,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>高棉</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -7016,12 +6962,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
+          <t>农民无需磨坊/TC即可存食；村民可驻房</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：农民工作速度+15%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：农民无需磨坊/TC即可存食</t>
         </is>
       </c>
     </row>
@@ -7031,7 +6977,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -7046,12 +6992,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>农民无需磨坊/TC即可存食；村民可驻房</t>
+          <t>大干道（所有黄金收入速度+10%；市场交易费降至10%）</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：农民无需磨坊/TC即可存食</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、行会；最直接一条：村民黑暗/封建/城堡/帝王费用-8/13/18/23%</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7007,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -7076,22 +7022,22 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>村民黑暗/封建/城堡/帝王费用-8/13/18/23%</t>
+          <t>猎人携带+15，猎物持续+20%；帝王人口+10</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、行会；最直接一条：村民黑暗/封建/城堡/帝王费用-8/13/18/23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：猎人携带+15，猎物持续+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="51" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -7106,22 +7052,22 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>猎人携带+15，猎物持续+20%；帝王人口+10</t>
+          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点；羊倌/猎人采食时缓慢产金</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：猎人携带+15，猎物持续+20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、双人锯；最直接一条：堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -7136,12 +7082,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点；羊倌/猎人采食时缓慢产金</t>
+          <t>猎人速度+40%；游牧（失去房屋时人口不减）</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 轮作、双人锯；最直接一条：堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、双人锯、行会；最直接一条：猎人速度+40%</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7097,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -7166,12 +7112,12 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>猎人速度+40%；游牧（失去房屋时人口不减）</t>
+          <t>市场贸易税仅5%</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、双人锯、行会；最直接一条：猎人速度+40%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、行会；最直接一条：市场贸易税仅5%</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7127,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -7196,22 +7142,22 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>市场贸易税仅5%；市场木材-100</t>
+          <t>码头提供的人口空间 +5；渔夫/捕鱼船携带+15；升时代木材+200</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、行会；最直接一条：市场贸易税仅5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 1 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、钻井采金法；最直接一条：码头提供的人口空间 +5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="51" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -7226,12 +7172,12 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>升时代木材+200；攻城武器木材-33%</t>
+          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 1 / 弱 0）；经济科技树 15/18；缺 轮作、采石场、钻井采金法；最直接一条：码头提供的人口空间 +5</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7187,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -7256,12 +7202,12 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>强化教堂使9格内村民效率+10%；阿兹瑙里骑兵（骑兵人口-20%）</t>
+          <t>农田升级食物+125%；初始石料+100</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 双人锯、钻井采金法；最直接一条：强化教堂使9格内村民效率+10%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：农田升级食物+125%</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7217,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -7286,12 +7232,12 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>初始黄金+50；圣物产生的黄金 +33%</t>
+          <t>羊倌工作速度+25%</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：村民携带量+3</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：羊倌工作速度+25%</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7247,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -7316,12 +7262,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>采果工存食+25%；聚落可训长矛/掷矛；骑兵杀敌+3黄金</t>
+          <t>村民黑暗移速+5%，封建起+10%</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：采果工存食+25%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：村民黑暗移速+5%，封建起+10%</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7292,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>兵营/攻城武器厂黄金升级-66%</t>
+          <t>捕鱼船/村民存食+5%；摧毁建筑抢25%资源</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -7361,7 +7307,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>雅典</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -7376,22 +7322,22 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>军役税（希腊步兵黄金50%改为额外食物）；TC可切换政策风格（经济/海军/军事）</t>
+          <t>牧场取代农田</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 1）；经济科技树 18/18（无缺项）；最直接一条：伐木工缓慢产食</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 14/18；缺 重犁、重犁升级、轮作、钻井采金法；最直接一条：牧场取代农田</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -7406,12 +7352,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）；攻城/防御工事升级木材-75%，研究+100%</t>
+          <t>纸币（伐木工产木并缓慢产金）；经济升级无木材且研究+100%</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 18/18（无缺项）；最直接一条：霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：纸币（伐木工产木并缓慢产金）</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7367,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -7436,12 +7382,12 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>建筑木材-15%</t>
+          <t>村民携带量+3；初始黄金+50；圣物产生的黄金 +33%</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：村民存金+10%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：村民携带量+3</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7397,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -7466,12 +7412,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>开局村民+1，食物-50；资源持续+15%</t>
+          <t>强化教堂使9格内村民效率+10%</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：开局村民+1，食物-50</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；经济科技树 16/18；缺 双人锯、钻井采金法；最直接一条：强化教堂使9格内村民效率+10%</t>
         </is>
       </c>
     </row>
@@ -7481,7 +7427,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -7496,12 +7442,12 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>采果工产食+木材</t>
+          <t>采果工存食+25%；聚落可训长矛/掷矛；骑兵杀敌+3黄金</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：采果工产食+木材</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：采果工存食+25%</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7457,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -7526,12 +7472,12 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>初始石料+100</t>
+          <t>采果工速度+15%</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：农田升级食物+125%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 1）；经济科技树 15/18；缺 双人锯、采石场、行会；最直接一条：采果工速度+15%</t>
         </is>
       </c>
     </row>
@@ -7541,7 +7487,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -7556,12 +7502,12 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>经济升级无木材且研究+100%</t>
+          <t>伐木工缓慢产食；军役税（希腊步兵黄金50%改为额外食物）</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：纸币（伐木工产木并缓慢产金）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 1）；经济科技树 18/18（无缺项）；最直接一条：伐木工缓慢产食</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7517,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>穆伊斯卡</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -7586,12 +7532,12 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>城堡起TC木材费用-50%</t>
+          <t>天然黄金资源持续时间 +15%</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：羊倌工作速度+25%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 0 / 弱 1）；经济科技树 18/18（无缺项）</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7547,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -7616,12 +7562,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>蝎式弩黄金-50%</t>
+          <t>村民存金+10%</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、采石场；最直接一条：村民收集/建造/修理速度+5%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：村民存金+10%</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7577,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -7646,12 +7592,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>强征兵役（生产民兵系消耗额外食物而非黄金）</t>
+          <t>资源持续+15%</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：养鱼场费用-33%且食物+200%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：开局村民+1，食物-50</t>
         </is>
       </c>
     </row>
@@ -7661,7 +7607,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -7676,12 +7622,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+          <t>采果工产食+木材</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：村民一击杀狼</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：采果工产食+木材</t>
         </is>
       </c>
     </row>
@@ -7691,7 +7637,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -7706,12 +7652,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>采果工速度+15%；王家敕令骑兵（骑马弩手黄金-40%）</t>
+          <t>村民收集/建造/修理速度+5%</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 1）；经济科技树 15/18；缺 双人锯、采石场、行会；最直接一条：采果工速度+15%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、采石场；最直接一条：村民收集/建造/修理速度+5%</t>
         </is>
       </c>
     </row>
@@ -7721,7 +7667,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -7736,12 +7682,12 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>村民黑暗移速+5%，封建起+10%</t>
+          <t>村民一击杀狼</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 双人锯；最直接一条：村民黑暗移速+5%，封建起+10%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：村民一击杀狼</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7697,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -7766,12 +7712,12 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>农田费用-40%</t>
+          <t>伐木工速度+15%</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：农田费用-40%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、双人锯；最直接一条：伐木工速度+15%</t>
         </is>
       </c>
     </row>
@@ -7781,7 +7727,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -7796,12 +7742,12 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>丝绸之路（贸易单位费用-50%）</t>
+          <t>伐木工产木+食物</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：丝绸之路（贸易单位费用-50%）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：伐木工产木+食物</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7757,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -7826,12 +7772,12 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>伐木工速度+15%</t>
+          <t>金矿工速度+25%</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、双人锯；最直接一条：伐木工速度+15%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：金矿工速度+25%</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7787,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -7856,12 +7802,12 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>伐木工产木+食物</t>
+          <t>初始木材/食物+50</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：伐木工产木+食物</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 18/18（无缺项）</t>
         </is>
       </c>
     </row>
@@ -7871,7 +7817,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -7886,12 +7832,12 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>金矿工速度+25%</t>
+          <t>升时代获得黄金+100、食物+100；哨站视野 +3 且不消耗石料</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 轮作、采石场；最直接一条：金矿工速度+25%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 17/18；缺 轮作</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7847,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -7916,12 +7862,12 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>每研究一次经济升级免费获一村民</t>
+          <t>牲畜驻磨坊被动产食</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：每研究一次经济升级免费获一村民</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 1）；经济科技树 16/18；缺 双人锯、行会</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7877,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -7946,12 +7892,12 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>升时代黄金-50%；篷车/行会免费</t>
+          <t>不需要房屋，但初始木材-100</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 0 / 弱 1）；经济科技树 18/18（无缺项）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 16/18；缺 轮作、采石场</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7907,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -7976,12 +7922,12 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>牧场取代农田</t>
+          <t>每座TC食物+100</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 14/18；缺 重犁、重犁升级、轮作、钻井采金法；最直接一条：牧场取代农田</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 钻井采金法</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7937,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -8006,12 +7952,12 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>初始木材/食物+50；波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
+          <t>磨坊/木料/采矿场建成后食物+35，石料+10</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 18/18（无缺项）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 采石场</t>
         </is>
       </c>
     </row>
@@ -8021,7 +7967,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -8036,12 +7982,12 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>升时代获得黄金+100、食物+100；哨站视野 +3 且不消耗石料</t>
+          <t>牧羊/捕鱼/狩猎也产黄金</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 17/18；缺 轮作</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 钻井采金法</t>
         </is>
       </c>
     </row>
@@ -8051,7 +7997,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -8066,12 +8012,12 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>铁匠铺/攻城武器厂科技食物费用-50%；TC石料费用-50%</t>
+          <t>军事建筑/码头建成后食物+55</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 17/18；缺 双人锯</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 轮作</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8027,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -8096,12 +8042,12 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>不需要房屋，但初始木材-100</t>
+          <t>每研究一次经济升级免费获一村民</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；经济科技树 16/18；缺 轮作、采石场</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：每研究一次经济升级免费获一村民</t>
         </is>
       </c>
     </row>
@@ -8111,7 +8057,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -8126,12 +8072,12 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>靶场/马厩木材-75</t>
+          <t>养鱼场费用-33%且食物+200%；强征兵役（生产民兵系消耗额外食物而非黄金）</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 采石场</t>
+          <t>阶段2·减费用；原生条目 3 条（强 1 / 弱 0）；经济科技树 16/18；缺 双人锯、行会；最直接一条：养鱼场费用-33%且食物+200%</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8087,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -8156,12 +8102,12 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>每座TC食物+100</t>
+          <t>靶场/马厩木材-75</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 钻井采金法</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 采石场</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8117,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -8186,12 +8132,12 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>磨坊/木料/采矿场建成后食物+35，石料+10</t>
+          <t>独轮推车/手推车免费</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 采石场</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；经济科技树 16/18；缺 采石场、行会；最直接一条：独轮推车/手推车免费</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8147,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -8216,12 +8162,12 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>牧羊/捕鱼/狩猎也产黄金</t>
+          <t>铁匠铺/攻城武器厂科技食物费用-50%；TC石料费用-50%</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 钻井采金法</t>
+          <t>阶段2·减费用；原生条目 2 条（强 0 / 弱 0）；经济科技树 17/18；缺 双人锯</t>
         </is>
       </c>
     </row>
@@ -8231,7 +8177,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -8246,12 +8192,12 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>军事建筑/码头建成后食物+55</t>
+          <t>伐木场科技免费</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；经济科技树 17/18；缺 轮作</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；经济科技树 17/18；缺 采石场</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8207,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -8276,12 +8222,12 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>刹帝利（军事单位食物-25%）</t>
+          <t>农田费用-40%</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 1）；经济科技树 16/18；缺 双人锯、行会</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：农田费用-40%</t>
         </is>
       </c>
     </row>
@@ -8291,7 +8237,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
@@ -8306,12 +8252,12 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>伐木场科技免费</t>
+          <t>丝绸之路（贸易单位费用-50%）</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；经济科技树 17/18；缺 采石场</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；经济科技树 17/18；缺 钻井采金法；最直接一条：丝绸之路（贸易单位费用-50%）</t>
         </is>
       </c>
     </row>
